--- a/LME/parser/cbr/data/cb_currency.xlsx
+++ b/LME/parser/cbr/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C913"/>
+  <dimension ref="A1:C914"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -10435,6 +10435,17 @@
       </c>
       <c r="C913">
         <v>84.2569</v>
+      </c>
+    </row>
+    <row r="914" spans="1:3">
+      <c r="A914" s="2">
+        <v>46280</v>
+      </c>
+      <c r="B914">
+        <v>1</v>
+      </c>
+      <c r="C914">
+        <v>84.33629999999999</v>
       </c>
     </row>
   </sheetData>
@@ -10444,7 +10455,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C913"/>
+  <dimension ref="A1:C914"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -20488,6 +20499,17 @@
       </c>
       <c r="C913">
         <v>97.8728</v>
+      </c>
+    </row>
+    <row r="914" spans="1:3">
+      <c r="A914" s="2">
+        <v>46280</v>
+      </c>
+      <c r="B914">
+        <v>1</v>
+      </c>
+      <c r="C914">
+        <v>97.76260000000001</v>
       </c>
     </row>
   </sheetData>
@@ -20497,7 +20519,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C913"/>
+  <dimension ref="A1:C914"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -30541,6 +30563,17 @@
       </c>
       <c r="C913">
         <v>60.429</v>
+      </c>
+    </row>
+    <row r="914" spans="1:3">
+      <c r="A914" s="2">
+        <v>46280</v>
+      </c>
+      <c r="B914">
+        <v>1</v>
+      </c>
+      <c r="C914">
+        <v>60.292</v>
       </c>
     </row>
   </sheetData>
@@ -30550,7 +30583,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C913"/>
+  <dimension ref="A1:C914"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -40594,6 +40627,17 @@
       </c>
       <c r="C913">
         <v>12.5519</v>
+      </c>
+    </row>
+    <row r="914" spans="1:3">
+      <c r="A914" s="2">
+        <v>46280</v>
+      </c>
+      <c r="B914">
+        <v>1</v>
+      </c>
+      <c r="C914">
+        <v>12.5353</v>
       </c>
     </row>
   </sheetData>
@@ -40603,7 +40647,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C913"/>
+  <dimension ref="A1:C914"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -50647,6 +50691,17 @@
       </c>
       <c r="C913">
         <v>114.008</v>
+      </c>
+    </row>
+    <row r="914" spans="1:3">
+      <c r="A914" s="2">
+        <v>46280</v>
+      </c>
+      <c r="B914">
+        <v>1</v>
+      </c>
+      <c r="C914">
+        <v>114.107</v>
       </c>
     </row>
   </sheetData>
@@ -50656,7 +50711,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C913"/>
+  <dimension ref="A1:C914"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -60700,6 +60755,17 @@
       </c>
       <c r="C913">
         <v>18.6909</v>
+      </c>
+    </row>
+    <row r="914" spans="1:3">
+      <c r="A914" s="2">
+        <v>46280</v>
+      </c>
+      <c r="B914">
+        <v>100</v>
+      </c>
+      <c r="C914">
+        <v>18.7036</v>
       </c>
     </row>
   </sheetData>
@@ -60709,7 +60775,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C913"/>
+  <dimension ref="A1:C914"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -70753,6 +70819,17 @@
       </c>
       <c r="C913">
         <v>54.5035</v>
+      </c>
+    </row>
+    <row r="914" spans="1:3">
+      <c r="A914" s="2">
+        <v>46280</v>
+      </c>
+      <c r="B914">
+        <v>100</v>
+      </c>
+      <c r="C914">
+        <v>54.8886</v>
       </c>
     </row>
   </sheetData>
@@ -70762,7 +70839,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C913"/>
+  <dimension ref="A1:C914"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -80808,6 +80885,17 @@
         <v>103.4843</v>
       </c>
     </row>
+    <row r="914" spans="1:3">
+      <c r="A914" s="2">
+        <v>46280</v>
+      </c>
+      <c r="B914">
+        <v>1</v>
+      </c>
+      <c r="C914">
+        <v>102.9873</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/cbr/data/cb_currency.xlsx
+++ b/LME/parser/cbr/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C914"/>
+  <dimension ref="A1:C915"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -10446,6 +10446,17 @@
       </c>
       <c r="C914">
         <v>84.33629999999999</v>
+      </c>
+    </row>
+    <row r="915" spans="1:3">
+      <c r="A915" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B915">
+        <v>1</v>
+      </c>
+      <c r="C915">
+        <v>84.2362</v>
       </c>
     </row>
   </sheetData>
@@ -10455,7 +10466,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C914"/>
+  <dimension ref="A1:C915"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -20510,6 +20521,17 @@
       </c>
       <c r="C914">
         <v>97.76260000000001</v>
+      </c>
+    </row>
+    <row r="915" spans="1:3">
+      <c r="A915" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B915">
+        <v>1</v>
+      </c>
+      <c r="C915">
+        <v>97.30119999999999</v>
       </c>
     </row>
   </sheetData>
@@ -20519,7 +20541,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C914"/>
+  <dimension ref="A1:C915"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -30574,6 +30596,17 @@
       </c>
       <c r="C914">
         <v>60.292</v>
+      </c>
+    </row>
+    <row r="915" spans="1:3">
+      <c r="A915" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B915">
+        <v>1</v>
+      </c>
+      <c r="C915">
+        <v>59.993</v>
       </c>
     </row>
   </sheetData>
@@ -30583,7 +30616,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C914"/>
+  <dimension ref="A1:C915"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -40638,6 +40671,17 @@
       </c>
       <c r="C914">
         <v>12.5353</v>
+      </c>
+    </row>
+    <row r="915" spans="1:3">
+      <c r="A915" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B915">
+        <v>1</v>
+      </c>
+      <c r="C915">
+        <v>12.5538</v>
       </c>
     </row>
   </sheetData>
@@ -40647,7 +40691,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C914"/>
+  <dimension ref="A1:C915"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -50702,6 +50746,17 @@
       </c>
       <c r="C914">
         <v>114.107</v>
+      </c>
+    </row>
+    <row r="915" spans="1:3">
+      <c r="A915" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B915">
+        <v>1</v>
+      </c>
+      <c r="C915">
+        <v>113.5167</v>
       </c>
     </row>
   </sheetData>
@@ -50711,7 +50766,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C914"/>
+  <dimension ref="A1:C915"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -60766,6 +60821,17 @@
       </c>
       <c r="C914">
         <v>18.7036</v>
+      </c>
+    </row>
+    <row r="915" spans="1:3">
+      <c r="A915" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B915">
+        <v>100</v>
+      </c>
+      <c r="C915">
+        <v>18.8111</v>
       </c>
     </row>
   </sheetData>
@@ -60775,7 +60841,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C914"/>
+  <dimension ref="A1:C915"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -70830,6 +70896,17 @@
       </c>
       <c r="C914">
         <v>54.8886</v>
+      </c>
+    </row>
+    <row r="915" spans="1:3">
+      <c r="A915" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B915">
+        <v>100</v>
+      </c>
+      <c r="C915">
+        <v>54.4689</v>
       </c>
     </row>
   </sheetData>
@@ -70839,7 +70916,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C914"/>
+  <dimension ref="A1:C915"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -80896,6 +80973,17 @@
         <v>102.9873</v>
       </c>
     </row>
+    <row r="915" spans="1:3">
+      <c r="A915" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B915">
+        <v>1</v>
+      </c>
+      <c r="C915">
+        <v>103.0286</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/cbr/data/cb_currency.xlsx
+++ b/LME/parser/cbr/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C915"/>
+  <dimension ref="A1:C916"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -10457,6 +10457,17 @@
       </c>
       <c r="C915">
         <v>84.2362</v>
+      </c>
+    </row>
+    <row r="916" spans="1:3">
+      <c r="A916" s="2">
+        <v>46282</v>
+      </c>
+      <c r="B916">
+        <v>1</v>
+      </c>
+      <c r="C916">
+        <v>84.17319999999999</v>
       </c>
     </row>
   </sheetData>
@@ -10466,7 +10477,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C915"/>
+  <dimension ref="A1:C916"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -20532,6 +20543,17 @@
       </c>
       <c r="C915">
         <v>97.30119999999999</v>
+      </c>
+    </row>
+    <row r="916" spans="1:3">
+      <c r="A916" s="2">
+        <v>46282</v>
+      </c>
+      <c r="B916">
+        <v>1</v>
+      </c>
+      <c r="C916">
+        <v>97.1275</v>
       </c>
     </row>
   </sheetData>
@@ -20541,7 +20563,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C915"/>
+  <dimension ref="A1:C916"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -30607,6 +30629,17 @@
       </c>
       <c r="C915">
         <v>59.993</v>
+      </c>
+    </row>
+    <row r="916" spans="1:3">
+      <c r="A916" s="2">
+        <v>46282</v>
+      </c>
+      <c r="B916">
+        <v>1</v>
+      </c>
+      <c r="C916">
+        <v>60.0407</v>
       </c>
     </row>
   </sheetData>
@@ -30616,7 +30649,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C915"/>
+  <dimension ref="A1:C916"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -40682,6 +40715,17 @@
       </c>
       <c r="C915">
         <v>12.5538</v>
+      </c>
+    </row>
+    <row r="916" spans="1:3">
+      <c r="A916" s="2">
+        <v>46282</v>
+      </c>
+      <c r="B916">
+        <v>1</v>
+      </c>
+      <c r="C916">
+        <v>12.5457</v>
       </c>
     </row>
   </sheetData>
@@ -40691,7 +40735,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C915"/>
+  <dimension ref="A1:C916"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -50757,6 +50801,17 @@
       </c>
       <c r="C915">
         <v>113.5167</v>
+      </c>
+    </row>
+    <row r="916" spans="1:3">
+      <c r="A916" s="2">
+        <v>46282</v>
+      </c>
+      <c r="B916">
+        <v>1</v>
+      </c>
+      <c r="C916">
+        <v>113.5328</v>
       </c>
     </row>
   </sheetData>
@@ -50766,7 +50821,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C915"/>
+  <dimension ref="A1:C916"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -60832,6 +60887,17 @@
       </c>
       <c r="C915">
         <v>18.8111</v>
+      </c>
+    </row>
+    <row r="916" spans="1:3">
+      <c r="A916" s="2">
+        <v>46282</v>
+      </c>
+      <c r="B916">
+        <v>100</v>
+      </c>
+      <c r="C916">
+        <v>18.7937</v>
       </c>
     </row>
   </sheetData>
@@ -60841,7 +60907,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C915"/>
+  <dimension ref="A1:C916"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -70907,6 +70973,17 @@
       </c>
       <c r="C915">
         <v>54.4689</v>
+      </c>
+    </row>
+    <row r="916" spans="1:3">
+      <c r="A916" s="2">
+        <v>46282</v>
+      </c>
+      <c r="B916">
+        <v>100</v>
+      </c>
+      <c r="C916">
+        <v>54.169</v>
       </c>
     </row>
   </sheetData>
@@ -70916,7 +70993,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C915"/>
+  <dimension ref="A1:C916"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -80984,6 +81061,17 @@
         <v>103.0286</v>
       </c>
     </row>
+    <row r="916" spans="1:3">
+      <c r="A916" s="2">
+        <v>46282</v>
+      </c>
+      <c r="B916">
+        <v>1</v>
+      </c>
+      <c r="C916">
+        <v>102.8007</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/cbr/data/cb_currency.xlsx
+++ b/LME/parser/cbr/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C916"/>
+  <dimension ref="A1:C917"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -10468,6 +10468,17 @@
       </c>
       <c r="C916">
         <v>84.17319999999999</v>
+      </c>
+    </row>
+    <row r="917" spans="1:3">
+      <c r="A917" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B917">
+        <v>1</v>
+      </c>
+      <c r="C917">
+        <v>84.5093</v>
       </c>
     </row>
   </sheetData>
@@ -10477,7 +10488,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C916"/>
+  <dimension ref="A1:C917"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -20554,6 +20565,17 @@
       </c>
       <c r="C916">
         <v>97.1275</v>
+      </c>
+    </row>
+    <row r="917" spans="1:3">
+      <c r="A917" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B917">
+        <v>1</v>
+      </c>
+      <c r="C917">
+        <v>97.4984</v>
       </c>
     </row>
   </sheetData>
@@ -20563,7 +20585,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C916"/>
+  <dimension ref="A1:C917"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -30640,6 +30662,17 @@
       </c>
       <c r="C916">
         <v>60.0407</v>
+      </c>
+    </row>
+    <row r="917" spans="1:3">
+      <c r="A917" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B917">
+        <v>1</v>
+      </c>
+      <c r="C917">
+        <v>60.0692</v>
       </c>
     </row>
   </sheetData>
@@ -30649,7 +30682,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C916"/>
+  <dimension ref="A1:C917"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -40726,6 +40759,17 @@
       </c>
       <c r="C916">
         <v>12.5457</v>
+      </c>
+    </row>
+    <row r="917" spans="1:3">
+      <c r="A917" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B917">
+        <v>1</v>
+      </c>
+      <c r="C917">
+        <v>12.5788</v>
       </c>
     </row>
   </sheetData>
@@ -40735,7 +40779,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C916"/>
+  <dimension ref="A1:C917"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -50812,6 +50856,17 @@
       </c>
       <c r="C916">
         <v>113.5328</v>
+      </c>
+    </row>
+    <row r="917" spans="1:3">
+      <c r="A917" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B917">
+        <v>1</v>
+      </c>
+      <c r="C917">
+        <v>113.6988</v>
       </c>
     </row>
   </sheetData>
@@ -50821,7 +50876,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C916"/>
+  <dimension ref="A1:C917"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -60898,6 +60953,17 @@
       </c>
       <c r="C916">
         <v>18.7937</v>
+      </c>
+    </row>
+    <row r="917" spans="1:3">
+      <c r="A917" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B917">
+        <v>100</v>
+      </c>
+      <c r="C917">
+        <v>18.996</v>
       </c>
     </row>
   </sheetData>
@@ -60907,7 +60973,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C916"/>
+  <dimension ref="A1:C917"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -70984,6 +71050,17 @@
       </c>
       <c r="C916">
         <v>54.169</v>
+      </c>
+    </row>
+    <row r="917" spans="1:3">
+      <c r="A917" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B917">
+        <v>100</v>
+      </c>
+      <c r="C917">
+        <v>54.1206</v>
       </c>
     </row>
   </sheetData>
@@ -70993,7 +71070,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C916"/>
+  <dimension ref="A1:C917"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -81072,6 +81149,17 @@
         <v>102.8007</v>
       </c>
     </row>
+    <row r="917" spans="1:3">
+      <c r="A917" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B917">
+        <v>1</v>
+      </c>
+      <c r="C917">
+        <v>102.3983</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/cbr/data/cb_currency.xlsx
+++ b/LME/parser/cbr/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C917"/>
+  <dimension ref="A1:C918"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -10479,6 +10479,17 @@
       </c>
       <c r="C917">
         <v>84.5093</v>
+      </c>
+    </row>
+    <row r="918" spans="1:3">
+      <c r="A918" s="2">
+        <v>46284</v>
+      </c>
+      <c r="B918">
+        <v>1</v>
+      </c>
+      <c r="C918">
+        <v>84.19750000000001</v>
       </c>
     </row>
   </sheetData>
@@ -10488,7 +10499,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C917"/>
+  <dimension ref="A1:C918"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -20576,6 +20587,17 @@
       </c>
       <c r="C917">
         <v>97.4984</v>
+      </c>
+    </row>
+    <row r="918" spans="1:3">
+      <c r="A918" s="2">
+        <v>46284</v>
+      </c>
+      <c r="B918">
+        <v>1</v>
+      </c>
+      <c r="C918">
+        <v>96.6671</v>
       </c>
     </row>
   </sheetData>
@@ -20585,7 +20607,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C917"/>
+  <dimension ref="A1:C918"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -30673,6 +30695,17 @@
       </c>
       <c r="C917">
         <v>60.0692</v>
+      </c>
+    </row>
+    <row r="918" spans="1:3">
+      <c r="A918" s="2">
+        <v>46284</v>
+      </c>
+      <c r="B918">
+        <v>1</v>
+      </c>
+      <c r="C918">
+        <v>59.9991</v>
       </c>
     </row>
   </sheetData>
@@ -30682,7 +30715,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C917"/>
+  <dimension ref="A1:C918"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -40770,6 +40803,17 @@
       </c>
       <c r="C917">
         <v>12.5788</v>
+      </c>
+    </row>
+    <row r="918" spans="1:3">
+      <c r="A918" s="2">
+        <v>46284</v>
+      </c>
+      <c r="B918">
+        <v>1</v>
+      </c>
+      <c r="C918">
+        <v>12.567</v>
       </c>
     </row>
   </sheetData>
@@ -40779,7 +40823,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C917"/>
+  <dimension ref="A1:C918"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -50867,6 +50911,17 @@
       </c>
       <c r="C917">
         <v>113.6988</v>
+      </c>
+    </row>
+    <row r="918" spans="1:3">
+      <c r="A918" s="2">
+        <v>46284</v>
+      </c>
+      <c r="B918">
+        <v>1</v>
+      </c>
+      <c r="C918">
+        <v>112.4289</v>
       </c>
     </row>
   </sheetData>
@@ -50876,7 +50931,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C917"/>
+  <dimension ref="A1:C918"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -60964,6 +61019,17 @@
       </c>
       <c r="C917">
         <v>18.996</v>
+      </c>
+    </row>
+    <row r="918" spans="1:3">
+      <c r="A918" s="2">
+        <v>46284</v>
+      </c>
+      <c r="B918">
+        <v>100</v>
+      </c>
+      <c r="C918">
+        <v>18.9387</v>
       </c>
     </row>
   </sheetData>
@@ -60973,7 +61039,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C917"/>
+  <dimension ref="A1:C918"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -71061,6 +71127,17 @@
       </c>
       <c r="C917">
         <v>54.1206</v>
+      </c>
+    </row>
+    <row r="918" spans="1:3">
+      <c r="A918" s="2">
+        <v>46284</v>
+      </c>
+      <c r="B918">
+        <v>100</v>
+      </c>
+      <c r="C918">
+        <v>53.5948</v>
       </c>
     </row>
   </sheetData>
@@ -71070,7 +71147,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C917"/>
+  <dimension ref="A1:C918"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -81160,6 +81237,17 @@
         <v>102.3983</v>
       </c>
     </row>
+    <row r="918" spans="1:3">
+      <c r="A918" s="2">
+        <v>46284</v>
+      </c>
+      <c r="B918">
+        <v>1</v>
+      </c>
+      <c r="C918">
+        <v>102.1071</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/cbr/data/cb_currency.xlsx
+++ b/LME/parser/cbr/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C918"/>
+  <dimension ref="A1:C919"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -10490,6 +10490,17 @@
       </c>
       <c r="C918">
         <v>84.19750000000001</v>
+      </c>
+    </row>
+    <row r="919" spans="1:3">
+      <c r="A919" s="2">
+        <v>46287</v>
+      </c>
+      <c r="B919">
+        <v>1</v>
+      </c>
+      <c r="C919">
+        <v>84.0954</v>
       </c>
     </row>
   </sheetData>
@@ -10499,7 +10510,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C918"/>
+  <dimension ref="A1:C919"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -20598,6 +20609,17 @@
       </c>
       <c r="C918">
         <v>96.6671</v>
+      </c>
+    </row>
+    <row r="919" spans="1:3">
+      <c r="A919" s="2">
+        <v>46287</v>
+      </c>
+      <c r="B919">
+        <v>1</v>
+      </c>
+      <c r="C919">
+        <v>96.3733</v>
       </c>
     </row>
   </sheetData>
@@ -20607,7 +20629,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C918"/>
+  <dimension ref="A1:C919"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -30706,6 +30728,17 @@
       </c>
       <c r="C918">
         <v>59.9991</v>
+      </c>
+    </row>
+    <row r="919" spans="1:3">
+      <c r="A919" s="2">
+        <v>46287</v>
+      </c>
+      <c r="B919">
+        <v>1</v>
+      </c>
+      <c r="C919">
+        <v>59.9096</v>
       </c>
     </row>
   </sheetData>
@@ -30715,7 +30748,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C918"/>
+  <dimension ref="A1:C919"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -40814,6 +40847,17 @@
       </c>
       <c r="C918">
         <v>12.567</v>
+      </c>
+    </row>
+    <row r="919" spans="1:3">
+      <c r="A919" s="2">
+        <v>46287</v>
+      </c>
+      <c r="B919">
+        <v>1</v>
+      </c>
+      <c r="C919">
+        <v>12.5448</v>
       </c>
     </row>
   </sheetData>
@@ -40823,7 +40867,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C918"/>
+  <dimension ref="A1:C919"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -50922,6 +50966,17 @@
       </c>
       <c r="C918">
         <v>112.4289</v>
+      </c>
+    </row>
+    <row r="919" spans="1:3">
+      <c r="A919" s="2">
+        <v>46287</v>
+      </c>
+      <c r="B919">
+        <v>1</v>
+      </c>
+      <c r="C919">
+        <v>112.3599</v>
       </c>
     </row>
   </sheetData>
@@ -50931,7 +50986,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C918"/>
+  <dimension ref="A1:C919"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -61030,6 +61085,17 @@
       </c>
       <c r="C918">
         <v>18.9387</v>
+      </c>
+    </row>
+    <row r="919" spans="1:3">
+      <c r="A919" s="2">
+        <v>46287</v>
+      </c>
+      <c r="B919">
+        <v>100</v>
+      </c>
+      <c r="C919">
+        <v>18.8318</v>
       </c>
     </row>
   </sheetData>
@@ -61039,7 +61105,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C918"/>
+  <dimension ref="A1:C919"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -71138,6 +71204,17 @@
       </c>
       <c r="C918">
         <v>53.5948</v>
+      </c>
+    </row>
+    <row r="919" spans="1:3">
+      <c r="A919" s="2">
+        <v>46287</v>
+      </c>
+      <c r="B919">
+        <v>100</v>
+      </c>
+      <c r="C919">
+        <v>53.5299</v>
       </c>
     </row>
   </sheetData>
@@ -71147,7 +71224,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C918"/>
+  <dimension ref="A1:C919"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -81248,6 +81325,17 @@
         <v>102.1071</v>
       </c>
     </row>
+    <row r="919" spans="1:3">
+      <c r="A919" s="2">
+        <v>46287</v>
+      </c>
+      <c r="B919">
+        <v>1</v>
+      </c>
+      <c r="C919">
+        <v>102.1443</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/cbr/data/cb_currency.xlsx
+++ b/LME/parser/cbr/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C919"/>
+  <dimension ref="A1:C920"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -10501,6 +10501,17 @@
       </c>
       <c r="C919">
         <v>84.0954</v>
+      </c>
+    </row>
+    <row r="920" spans="1:3">
+      <c r="A920" s="2">
+        <v>46288</v>
+      </c>
+      <c r="B920">
+        <v>1</v>
+      </c>
+      <c r="C920">
+        <v>84.06570000000001</v>
       </c>
     </row>
   </sheetData>
@@ -10510,7 +10521,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C919"/>
+  <dimension ref="A1:C920"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -20620,6 +20631,17 @@
       </c>
       <c r="C919">
         <v>96.3733</v>
+      </c>
+    </row>
+    <row r="920" spans="1:3">
+      <c r="A920" s="2">
+        <v>46288</v>
+      </c>
+      <c r="B920">
+        <v>1</v>
+      </c>
+      <c r="C920">
+        <v>96.5915</v>
       </c>
     </row>
   </sheetData>
@@ -20629,7 +20651,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C919"/>
+  <dimension ref="A1:C920"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -30739,6 +30761,17 @@
       </c>
       <c r="C919">
         <v>59.9096</v>
+      </c>
+    </row>
+    <row r="920" spans="1:3">
+      <c r="A920" s="2">
+        <v>46288</v>
+      </c>
+      <c r="B920">
+        <v>1</v>
+      </c>
+      <c r="C920">
+        <v>59.88</v>
       </c>
     </row>
   </sheetData>
@@ -30748,7 +30781,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C919"/>
+  <dimension ref="A1:C920"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -40858,6 +40891,17 @@
       </c>
       <c r="C919">
         <v>12.5448</v>
+      </c>
+    </row>
+    <row r="920" spans="1:3">
+      <c r="A920" s="2">
+        <v>46288</v>
+      </c>
+      <c r="B920">
+        <v>1</v>
+      </c>
+      <c r="C920">
+        <v>12.5291</v>
       </c>
     </row>
   </sheetData>
@@ -40867,7 +40911,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C919"/>
+  <dimension ref="A1:C920"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -50977,6 +51021,17 @@
       </c>
       <c r="C919">
         <v>112.3599</v>
+      </c>
+    </row>
+    <row r="920" spans="1:3">
+      <c r="A920" s="2">
+        <v>46288</v>
+      </c>
+      <c r="B920">
+        <v>1</v>
+      </c>
+      <c r="C920">
+        <v>112.4295</v>
       </c>
     </row>
   </sheetData>
@@ -50986,7 +51041,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C919"/>
+  <dimension ref="A1:C920"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -61096,6 +61151,17 @@
       </c>
       <c r="C919">
         <v>18.8318</v>
+      </c>
+    </row>
+    <row r="920" spans="1:3">
+      <c r="A920" s="2">
+        <v>46288</v>
+      </c>
+      <c r="B920">
+        <v>100</v>
+      </c>
+      <c r="C920">
+        <v>18.7463</v>
       </c>
     </row>
   </sheetData>
@@ -61105,7 +61171,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C919"/>
+  <dimension ref="A1:C920"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -71215,6 +71281,17 @@
       </c>
       <c r="C919">
         <v>53.5299</v>
+      </c>
+    </row>
+    <row r="920" spans="1:3">
+      <c r="A920" s="2">
+        <v>46288</v>
+      </c>
+      <c r="B920">
+        <v>100</v>
+      </c>
+      <c r="C920">
+        <v>53.5109</v>
       </c>
     </row>
   </sheetData>
@@ -71224,7 +71301,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C919"/>
+  <dimension ref="A1:C920"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -81336,6 +81413,17 @@
         <v>102.1443</v>
       </c>
     </row>
+    <row r="920" spans="1:3">
+      <c r="A920" s="2">
+        <v>46288</v>
+      </c>
+      <c r="B920">
+        <v>1</v>
+      </c>
+      <c r="C920">
+        <v>102.4442</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/cbr/data/cb_currency.xlsx
+++ b/LME/parser/cbr/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C920"/>
+  <dimension ref="A1:C921"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -10512,6 +10512,17 @@
       </c>
       <c r="C920">
         <v>84.06570000000001</v>
+      </c>
+    </row>
+    <row r="921" spans="1:3">
+      <c r="A921" s="2">
+        <v>46289</v>
+      </c>
+      <c r="B921">
+        <v>1</v>
+      </c>
+      <c r="C921">
+        <v>84.3969</v>
       </c>
     </row>
   </sheetData>
@@ -10521,7 +10532,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C920"/>
+  <dimension ref="A1:C921"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -20642,6 +20653,17 @@
       </c>
       <c r="C920">
         <v>96.5915</v>
+      </c>
+    </row>
+    <row r="921" spans="1:3">
+      <c r="A921" s="2">
+        <v>46289</v>
+      </c>
+      <c r="B921">
+        <v>1</v>
+      </c>
+      <c r="C921">
+        <v>96.74420000000001</v>
       </c>
     </row>
   </sheetData>
@@ -20651,7 +20673,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C920"/>
+  <dimension ref="A1:C921"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -30772,6 +30794,17 @@
       </c>
       <c r="C920">
         <v>59.88</v>
+      </c>
+    </row>
+    <row r="921" spans="1:3">
+      <c r="A921" s="2">
+        <v>46289</v>
+      </c>
+      <c r="B921">
+        <v>1</v>
+      </c>
+      <c r="C921">
+        <v>59.9387</v>
       </c>
     </row>
   </sheetData>
@@ -30781,7 +30814,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C920"/>
+  <dimension ref="A1:C921"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -40902,6 +40935,17 @@
       </c>
       <c r="C920">
         <v>12.5291</v>
+      </c>
+    </row>
+    <row r="921" spans="1:3">
+      <c r="A921" s="2">
+        <v>46289</v>
+      </c>
+      <c r="B921">
+        <v>1</v>
+      </c>
+      <c r="C921">
+        <v>12.5598</v>
       </c>
     </row>
   </sheetData>
@@ -40911,7 +40955,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C920"/>
+  <dimension ref="A1:C921"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -51032,6 +51076,17 @@
       </c>
       <c r="C920">
         <v>112.4295</v>
+      </c>
+    </row>
+    <row r="921" spans="1:3">
+      <c r="A921" s="2">
+        <v>46289</v>
+      </c>
+      <c r="B921">
+        <v>1</v>
+      </c>
+      <c r="C921">
+        <v>112.653</v>
       </c>
     </row>
   </sheetData>
@@ -51041,7 +51096,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C920"/>
+  <dimension ref="A1:C921"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -61162,6 +61217,17 @@
       </c>
       <c r="C920">
         <v>18.7463</v>
+      </c>
+    </row>
+    <row r="921" spans="1:3">
+      <c r="A921" s="2">
+        <v>46289</v>
+      </c>
+      <c r="B921">
+        <v>100</v>
+      </c>
+      <c r="C921">
+        <v>18.8449</v>
       </c>
     </row>
   </sheetData>
@@ -61171,7 +61237,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C920"/>
+  <dimension ref="A1:C921"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -71292,6 +71358,17 @@
       </c>
       <c r="C920">
         <v>53.5109</v>
+      </c>
+    </row>
+    <row r="921" spans="1:3">
+      <c r="A921" s="2">
+        <v>46289</v>
+      </c>
+      <c r="B921">
+        <v>100</v>
+      </c>
+      <c r="C921">
+        <v>53.7218</v>
       </c>
     </row>
   </sheetData>
@@ -71301,7 +71378,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C920"/>
+  <dimension ref="A1:C921"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -81424,6 +81501,17 @@
         <v>102.4442</v>
       </c>
     </row>
+    <row r="921" spans="1:3">
+      <c r="A921" s="2">
+        <v>46289</v>
+      </c>
+      <c r="B921">
+        <v>1</v>
+      </c>
+      <c r="C921">
+        <v>102.6477</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/cbr/data/cb_currency.xlsx
+++ b/LME/parser/cbr/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C921"/>
+  <dimension ref="A1:C922"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -10523,6 +10523,17 @@
       </c>
       <c r="C921">
         <v>84.3969</v>
+      </c>
+    </row>
+    <row r="922" spans="1:3">
+      <c r="A922" s="2">
+        <v>46290</v>
+      </c>
+      <c r="B922">
+        <v>1</v>
+      </c>
+      <c r="C922">
+        <v>84.9057</v>
       </c>
     </row>
   </sheetData>
@@ -10532,7 +10543,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C921"/>
+  <dimension ref="A1:C922"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -20664,6 +20675,17 @@
       </c>
       <c r="C921">
         <v>96.74420000000001</v>
+      </c>
+    </row>
+    <row r="922" spans="1:3">
+      <c r="A922" s="2">
+        <v>46290</v>
+      </c>
+      <c r="B922">
+        <v>1</v>
+      </c>
+      <c r="C922">
+        <v>96.88590000000001</v>
       </c>
     </row>
   </sheetData>
@@ -20673,7 +20695,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C921"/>
+  <dimension ref="A1:C922"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -30805,6 +30827,17 @@
       </c>
       <c r="C921">
         <v>59.9387</v>
+      </c>
+    </row>
+    <row r="922" spans="1:3">
+      <c r="A922" s="2">
+        <v>46290</v>
+      </c>
+      <c r="B922">
+        <v>1</v>
+      </c>
+      <c r="C922">
+        <v>59.7057</v>
       </c>
     </row>
   </sheetData>
@@ -30814,7 +30847,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C921"/>
+  <dimension ref="A1:C922"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -40946,6 +40979,17 @@
       </c>
       <c r="C921">
         <v>12.5598</v>
+      </c>
+    </row>
+    <row r="922" spans="1:3">
+      <c r="A922" s="2">
+        <v>46290</v>
+      </c>
+      <c r="B922">
+        <v>1</v>
+      </c>
+      <c r="C922">
+        <v>12.65</v>
       </c>
     </row>
   </sheetData>
@@ -40955,7 +40999,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C921"/>
+  <dimension ref="A1:C922"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -51087,6 +51131,17 @@
       </c>
       <c r="C921">
         <v>112.653</v>
+      </c>
+    </row>
+    <row r="922" spans="1:3">
+      <c r="A922" s="2">
+        <v>46290</v>
+      </c>
+      <c r="B922">
+        <v>1</v>
+      </c>
+      <c r="C922">
+        <v>112.6274</v>
       </c>
     </row>
   </sheetData>
@@ -51096,7 +51151,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C921"/>
+  <dimension ref="A1:C922"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -61228,6 +61283,17 @@
       </c>
       <c r="C921">
         <v>18.8449</v>
+      </c>
+    </row>
+    <row r="922" spans="1:3">
+      <c r="A922" s="2">
+        <v>46290</v>
+      </c>
+      <c r="B922">
+        <v>100</v>
+      </c>
+      <c r="C922">
+        <v>19.0521</v>
       </c>
     </row>
   </sheetData>
@@ -61237,7 +61303,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C921"/>
+  <dimension ref="A1:C922"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -71369,6 +71435,17 @@
       </c>
       <c r="C921">
         <v>53.7218</v>
+      </c>
+    </row>
+    <row r="922" spans="1:3">
+      <c r="A922" s="2">
+        <v>46290</v>
+      </c>
+      <c r="B922">
+        <v>100</v>
+      </c>
+      <c r="C922">
+        <v>53.7514</v>
       </c>
     </row>
   </sheetData>
@@ -71378,7 +71455,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C921"/>
+  <dimension ref="A1:C922"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -81512,6 +81589,17 @@
         <v>102.6477</v>
       </c>
     </row>
+    <row r="922" spans="1:3">
+      <c r="A922" s="2">
+        <v>46290</v>
+      </c>
+      <c r="B922">
+        <v>1</v>
+      </c>
+      <c r="C922">
+        <v>102.5679</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/cbr/data/cb_currency.xlsx
+++ b/LME/parser/cbr/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C922"/>
+  <dimension ref="A1:C923"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -10534,6 +10534,17 @@
       </c>
       <c r="C922">
         <v>84.9057</v>
+      </c>
+    </row>
+    <row r="923" spans="1:3">
+      <c r="A923" s="2">
+        <v>46291</v>
+      </c>
+      <c r="B923">
+        <v>1</v>
+      </c>
+      <c r="C923">
+        <v>84.34139999999999</v>
       </c>
     </row>
   </sheetData>
@@ -10543,7 +10554,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C922"/>
+  <dimension ref="A1:C923"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -20686,6 +20697,17 @@
       </c>
       <c r="C922">
         <v>96.88590000000001</v>
+      </c>
+    </row>
+    <row r="923" spans="1:3">
+      <c r="A923" s="2">
+        <v>46291</v>
+      </c>
+      <c r="B923">
+        <v>1</v>
+      </c>
+      <c r="C923">
+        <v>95.87090000000001</v>
       </c>
     </row>
   </sheetData>
@@ -20695,7 +20717,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C922"/>
+  <dimension ref="A1:C923"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -30838,6 +30860,17 @@
       </c>
       <c r="C922">
         <v>59.7057</v>
+      </c>
+    </row>
+    <row r="923" spans="1:3">
+      <c r="A923" s="2">
+        <v>46291</v>
+      </c>
+      <c r="B923">
+        <v>1</v>
+      </c>
+      <c r="C923">
+        <v>59.1992</v>
       </c>
     </row>
   </sheetData>
@@ -30847,7 +30880,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C922"/>
+  <dimension ref="A1:C923"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -40990,6 +41023,17 @@
       </c>
       <c r="C922">
         <v>12.65</v>
+      </c>
+    </row>
+    <row r="923" spans="1:3">
+      <c r="A923" s="2">
+        <v>46291</v>
+      </c>
+      <c r="B923">
+        <v>1</v>
+      </c>
+      <c r="C923">
+        <v>12.5355</v>
       </c>
     </row>
   </sheetData>
@@ -40999,7 +41043,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C922"/>
+  <dimension ref="A1:C923"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -51142,6 +51186,17 @@
       </c>
       <c r="C922">
         <v>112.6274</v>
+      </c>
+    </row>
+    <row r="923" spans="1:3">
+      <c r="A923" s="2">
+        <v>46291</v>
+      </c>
+      <c r="B923">
+        <v>1</v>
+      </c>
+      <c r="C923">
+        <v>111.4993</v>
       </c>
     </row>
   </sheetData>
@@ -51151,7 +51206,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C922"/>
+  <dimension ref="A1:C923"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -61294,6 +61349,17 @@
       </c>
       <c r="C922">
         <v>19.0521</v>
+      </c>
+    </row>
+    <row r="923" spans="1:3">
+      <c r="A923" s="2">
+        <v>46291</v>
+      </c>
+      <c r="B923">
+        <v>100</v>
+      </c>
+      <c r="C923">
+        <v>19.0865</v>
       </c>
     </row>
   </sheetData>
@@ -61303,7 +61369,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C922"/>
+  <dimension ref="A1:C923"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -71446,6 +71512,17 @@
       </c>
       <c r="C922">
         <v>53.7514</v>
+      </c>
+    </row>
+    <row r="923" spans="1:3">
+      <c r="A923" s="2">
+        <v>46291</v>
+      </c>
+      <c r="B923">
+        <v>100</v>
+      </c>
+      <c r="C923">
+        <v>53.1351</v>
       </c>
     </row>
   </sheetData>
@@ -71455,7 +71532,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C922"/>
+  <dimension ref="A1:C923"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -81600,6 +81677,17 @@
         <v>102.5679</v>
       </c>
     </row>
+    <row r="923" spans="1:3">
+      <c r="A923" s="2">
+        <v>46291</v>
+      </c>
+      <c r="B923">
+        <v>1</v>
+      </c>
+      <c r="C923">
+        <v>101.7756</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/cbr/data/cb_currency.xlsx
+++ b/LME/parser/cbr/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C923"/>
+  <dimension ref="A1:C924"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -10545,6 +10545,17 @@
       </c>
       <c r="C923">
         <v>84.34139999999999</v>
+      </c>
+    </row>
+    <row r="924" spans="1:3">
+      <c r="A924" s="2">
+        <v>46294</v>
+      </c>
+      <c r="B924">
+        <v>1</v>
+      </c>
+      <c r="C924">
+        <v>84.4075</v>
       </c>
     </row>
   </sheetData>
@@ -10554,7 +10565,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C923"/>
+  <dimension ref="A1:C924"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -20708,6 +20719,17 @@
       </c>
       <c r="C923">
         <v>95.87090000000001</v>
+      </c>
+    </row>
+    <row r="924" spans="1:3">
+      <c r="A924" s="2">
+        <v>46294</v>
+      </c>
+      <c r="B924">
+        <v>1</v>
+      </c>
+      <c r="C924">
+        <v>96.2499</v>
       </c>
     </row>
   </sheetData>
@@ -20717,7 +20739,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C923"/>
+  <dimension ref="A1:C924"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -30871,6 +30893,17 @@
       </c>
       <c r="C923">
         <v>59.1992</v>
+      </c>
+    </row>
+    <row r="924" spans="1:3">
+      <c r="A924" s="2">
+        <v>46294</v>
+      </c>
+      <c r="B924">
+        <v>1</v>
+      </c>
+      <c r="C924">
+        <v>59.2794</v>
       </c>
     </row>
   </sheetData>
@@ -30880,7 +30913,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C923"/>
+  <dimension ref="A1:C924"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -41034,6 +41067,17 @@
       </c>
       <c r="C923">
         <v>12.5355</v>
+      </c>
+    </row>
+    <row r="924" spans="1:3">
+      <c r="A924" s="2">
+        <v>46294</v>
+      </c>
+      <c r="B924">
+        <v>1</v>
+      </c>
+      <c r="C924">
+        <v>12.5629</v>
       </c>
     </row>
   </sheetData>
@@ -41043,7 +41087,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C923"/>
+  <dimension ref="A1:C924"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -51197,6 +51241,17 @@
       </c>
       <c r="C923">
         <v>111.4993</v>
+      </c>
+    </row>
+    <row r="924" spans="1:3">
+      <c r="A924" s="2">
+        <v>46294</v>
+      </c>
+      <c r="B924">
+        <v>1</v>
+      </c>
+      <c r="C924">
+        <v>111.8062</v>
       </c>
     </row>
   </sheetData>
@@ -51206,7 +51261,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C923"/>
+  <dimension ref="A1:C924"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -61360,6 +61415,17 @@
       </c>
       <c r="C923">
         <v>19.0865</v>
+      </c>
+    </row>
+    <row r="924" spans="1:3">
+      <c r="A924" s="2">
+        <v>46294</v>
+      </c>
+      <c r="B924">
+        <v>100</v>
+      </c>
+      <c r="C924">
+        <v>19.1019</v>
       </c>
     </row>
   </sheetData>
@@ -61369,7 +61435,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C923"/>
+  <dimension ref="A1:C924"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -71523,6 +71589,17 @@
       </c>
       <c r="C923">
         <v>53.1351</v>
+      </c>
+    </row>
+    <row r="924" spans="1:3">
+      <c r="A924" s="2">
+        <v>46294</v>
+      </c>
+      <c r="B924">
+        <v>100</v>
+      </c>
+      <c r="C924">
+        <v>53.5071</v>
       </c>
     </row>
   </sheetData>
@@ -71532,7 +71609,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C923"/>
+  <dimension ref="A1:C924"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -81688,6 +81765,17 @@
         <v>101.7756</v>
       </c>
     </row>
+    <row r="924" spans="1:3">
+      <c r="A924" s="2">
+        <v>46294</v>
+      </c>
+      <c r="B924">
+        <v>1</v>
+      </c>
+      <c r="C924">
+        <v>101.5612</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/cbr/data/cb_currency.xlsx
+++ b/LME/parser/cbr/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C924"/>
+  <dimension ref="A1:C925"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -10556,6 +10556,17 @@
       </c>
       <c r="C924">
         <v>84.4075</v>
+      </c>
+    </row>
+    <row r="925" spans="1:3">
+      <c r="A925" s="2">
+        <v>46295</v>
+      </c>
+      <c r="B925">
+        <v>1</v>
+      </c>
+      <c r="C925">
+        <v>84.42829999999999</v>
       </c>
     </row>
   </sheetData>
@@ -10565,7 +10576,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C924"/>
+  <dimension ref="A1:C925"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -20730,6 +20741,17 @@
       </c>
       <c r="C924">
         <v>96.2499</v>
+      </c>
+    </row>
+    <row r="925" spans="1:3">
+      <c r="A925" s="2">
+        <v>46295</v>
+      </c>
+      <c r="B925">
+        <v>1</v>
+      </c>
+      <c r="C925">
+        <v>96.0625</v>
       </c>
     </row>
   </sheetData>
@@ -20739,7 +20761,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C924"/>
+  <dimension ref="A1:C925"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -30904,6 +30926,17 @@
       </c>
       <c r="C924">
         <v>59.2794</v>
+      </c>
+    </row>
+    <row r="925" spans="1:3">
+      <c r="A925" s="2">
+        <v>46295</v>
+      </c>
+      <c r="B925">
+        <v>1</v>
+      </c>
+      <c r="C925">
+        <v>58.9901</v>
       </c>
     </row>
   </sheetData>
@@ -30913,7 +30946,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C924"/>
+  <dimension ref="A1:C925"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -41078,6 +41111,17 @@
       </c>
       <c r="C924">
         <v>12.5629</v>
+      </c>
+    </row>
+    <row r="925" spans="1:3">
+      <c r="A925" s="2">
+        <v>46295</v>
+      </c>
+      <c r="B925">
+        <v>1</v>
+      </c>
+      <c r="C925">
+        <v>12.5764</v>
       </c>
     </row>
   </sheetData>
@@ -41087,7 +41131,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C924"/>
+  <dimension ref="A1:C925"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -51252,6 +51296,17 @@
       </c>
       <c r="C924">
         <v>111.8062</v>
+      </c>
+    </row>
+    <row r="925" spans="1:3">
+      <c r="A925" s="2">
+        <v>46295</v>
+      </c>
+      <c r="B925">
+        <v>1</v>
+      </c>
+      <c r="C925">
+        <v>111.8759</v>
       </c>
     </row>
   </sheetData>
@@ -51261,7 +51316,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C924"/>
+  <dimension ref="A1:C925"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -61426,6 +61481,17 @@
       </c>
       <c r="C924">
         <v>19.1019</v>
+      </c>
+    </row>
+    <row r="925" spans="1:3">
+      <c r="A925" s="2">
+        <v>46295</v>
+      </c>
+      <c r="B925">
+        <v>100</v>
+      </c>
+      <c r="C925">
+        <v>19.1114</v>
       </c>
     </row>
   </sheetData>
@@ -61435,7 +61501,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C924"/>
+  <dimension ref="A1:C925"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -71600,6 +71666,17 @@
       </c>
       <c r="C924">
         <v>53.5071</v>
+      </c>
+    </row>
+    <row r="925" spans="1:3">
+      <c r="A925" s="2">
+        <v>46295</v>
+      </c>
+      <c r="B925">
+        <v>100</v>
+      </c>
+      <c r="C925">
+        <v>53.6325</v>
       </c>
     </row>
   </sheetData>
@@ -71609,7 +71686,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C924"/>
+  <dimension ref="A1:C925"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -81776,6 +81853,17 @@
         <v>101.5612</v>
       </c>
     </row>
+    <row r="925" spans="1:3">
+      <c r="A925" s="2">
+        <v>46295</v>
+      </c>
+      <c r="B925">
+        <v>1</v>
+      </c>
+      <c r="C925">
+        <v>101.2208</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/cbr/data/cb_currency.xlsx
+++ b/LME/parser/cbr/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C925"/>
+  <dimension ref="A1:C926"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -10567,6 +10567,17 @@
       </c>
       <c r="C925">
         <v>84.42829999999999</v>
+      </c>
+    </row>
+    <row r="926" spans="1:3">
+      <c r="A926" s="2">
+        <v>46296</v>
+      </c>
+      <c r="B926">
+        <v>1</v>
+      </c>
+      <c r="C926">
+        <v>83.55880000000001</v>
       </c>
     </row>
   </sheetData>
@@ -10576,7 +10587,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C925"/>
+  <dimension ref="A1:C926"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -20752,6 +20763,17 @@
       </c>
       <c r="C925">
         <v>96.0625</v>
+      </c>
+    </row>
+    <row r="926" spans="1:3">
+      <c r="A926" s="2">
+        <v>46296</v>
+      </c>
+      <c r="B926">
+        <v>1</v>
+      </c>
+      <c r="C926">
+        <v>94.881</v>
       </c>
     </row>
   </sheetData>
@@ -20761,7 +20783,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C925"/>
+  <dimension ref="A1:C926"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -30937,6 +30959,17 @@
       </c>
       <c r="C925">
         <v>58.9901</v>
+      </c>
+    </row>
+    <row r="926" spans="1:3">
+      <c r="A926" s="2">
+        <v>46296</v>
+      </c>
+      <c r="B926">
+        <v>1</v>
+      </c>
+      <c r="C926">
+        <v>58.299</v>
       </c>
     </row>
   </sheetData>
@@ -30946,7 +30979,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C925"/>
+  <dimension ref="A1:C926"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -41122,6 +41155,17 @@
       </c>
       <c r="C925">
         <v>12.5764</v>
+      </c>
+    </row>
+    <row r="926" spans="1:3">
+      <c r="A926" s="2">
+        <v>46296</v>
+      </c>
+      <c r="B926">
+        <v>1</v>
+      </c>
+      <c r="C926">
+        <v>12.4732</v>
       </c>
     </row>
   </sheetData>
@@ -41131,7 +41175,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C925"/>
+  <dimension ref="A1:C926"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -51307,6 +51351,17 @@
       </c>
       <c r="C925">
         <v>111.8759</v>
+      </c>
+    </row>
+    <row r="926" spans="1:3">
+      <c r="A926" s="2">
+        <v>46296</v>
+      </c>
+      <c r="B926">
+        <v>1</v>
+      </c>
+      <c r="C926">
+        <v>110.4146</v>
       </c>
     </row>
   </sheetData>
@@ -51316,7 +51371,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C925"/>
+  <dimension ref="A1:C926"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -61492,6 +61547,17 @@
       </c>
       <c r="C925">
         <v>19.1114</v>
+      </c>
+    </row>
+    <row r="926" spans="1:3">
+      <c r="A926" s="2">
+        <v>46296</v>
+      </c>
+      <c r="B926">
+        <v>100</v>
+      </c>
+      <c r="C926">
+        <v>19.0179</v>
       </c>
     </row>
   </sheetData>
@@ -61501,7 +61567,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C925"/>
+  <dimension ref="A1:C926"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -71677,6 +71743,17 @@
       </c>
       <c r="C925">
         <v>53.6325</v>
+      </c>
+    </row>
+    <row r="926" spans="1:3">
+      <c r="A926" s="2">
+        <v>46296</v>
+      </c>
+      <c r="B926">
+        <v>100</v>
+      </c>
+      <c r="C926">
+        <v>53.1038</v>
       </c>
     </row>
   </sheetData>
@@ -71686,7 +71763,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C925"/>
+  <dimension ref="A1:C926"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -81864,6 +81941,17 @@
         <v>101.2208</v>
       </c>
     </row>
+    <row r="926" spans="1:3">
+      <c r="A926" s="2">
+        <v>46296</v>
+      </c>
+      <c r="B926">
+        <v>1</v>
+      </c>
+      <c r="C926">
+        <v>100.3348</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/cbr/data/cb_currency.xlsx
+++ b/LME/parser/cbr/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C926"/>
+  <dimension ref="A1:C927"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -10578,6 +10578,17 @@
       </c>
       <c r="C926">
         <v>83.55880000000001</v>
+      </c>
+    </row>
+    <row r="927" spans="1:3">
+      <c r="A927" s="2">
+        <v>46297</v>
+      </c>
+      <c r="B927">
+        <v>1</v>
+      </c>
+      <c r="C927">
+        <v>83.2454</v>
       </c>
     </row>
   </sheetData>
@@ -10587,7 +10598,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C926"/>
+  <dimension ref="A1:C927"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -20774,6 +20785,17 @@
       </c>
       <c r="C926">
         <v>94.881</v>
+      </c>
+    </row>
+    <row r="927" spans="1:3">
+      <c r="A927" s="2">
+        <v>46297</v>
+      </c>
+      <c r="B927">
+        <v>1</v>
+      </c>
+      <c r="C927">
+        <v>94.5252</v>
       </c>
     </row>
   </sheetData>
@@ -20783,7 +20805,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C926"/>
+  <dimension ref="A1:C927"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -30970,6 +30992,17 @@
       </c>
       <c r="C926">
         <v>58.299</v>
+      </c>
+    </row>
+    <row r="927" spans="1:3">
+      <c r="A927" s="2">
+        <v>46297</v>
+      </c>
+      <c r="B927">
+        <v>1</v>
+      </c>
+      <c r="C927">
+        <v>57.8472</v>
       </c>
     </row>
   </sheetData>
@@ -30979,7 +31012,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C926"/>
+  <dimension ref="A1:C927"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -41166,6 +41199,17 @@
       </c>
       <c r="C926">
         <v>12.4732</v>
+      </c>
+    </row>
+    <row r="927" spans="1:3">
+      <c r="A927" s="2">
+        <v>46297</v>
+      </c>
+      <c r="B927">
+        <v>1</v>
+      </c>
+      <c r="C927">
+        <v>12.4028</v>
       </c>
     </row>
   </sheetData>
@@ -41175,7 +41219,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C926"/>
+  <dimension ref="A1:C927"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -51362,6 +51406,17 @@
       </c>
       <c r="C926">
         <v>110.4146</v>
+      </c>
+    </row>
+    <row r="927" spans="1:3">
+      <c r="A927" s="2">
+        <v>46297</v>
+      </c>
+      <c r="B927">
+        <v>1</v>
+      </c>
+      <c r="C927">
+        <v>110.5915</v>
       </c>
     </row>
   </sheetData>
@@ -51371,7 +51426,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C926"/>
+  <dimension ref="A1:C927"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -61558,6 +61613,17 @@
       </c>
       <c r="C926">
         <v>19.0179</v>
+      </c>
+    </row>
+    <row r="927" spans="1:3">
+      <c r="A927" s="2">
+        <v>46297</v>
+      </c>
+      <c r="B927">
+        <v>100</v>
+      </c>
+      <c r="C927">
+        <v>18.8825</v>
       </c>
     </row>
   </sheetData>
@@ -61567,7 +61633,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C926"/>
+  <dimension ref="A1:C927"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -71754,6 +71820,17 @@
       </c>
       <c r="C926">
         <v>53.1038</v>
+      </c>
+    </row>
+    <row r="927" spans="1:3">
+      <c r="A927" s="2">
+        <v>46297</v>
+      </c>
+      <c r="B927">
+        <v>100</v>
+      </c>
+      <c r="C927">
+        <v>52.637</v>
       </c>
     </row>
   </sheetData>
@@ -71763,7 +71840,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C926"/>
+  <dimension ref="A1:C927"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -81952,6 +82029,17 @@
         <v>100.3348</v>
       </c>
     </row>
+    <row r="927" spans="1:3">
+      <c r="A927" s="2">
+        <v>46297</v>
+      </c>
+      <c r="B927">
+        <v>1</v>
+      </c>
+      <c r="C927">
+        <v>99.6593</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/cbr/data/cb_currency.xlsx
+++ b/LME/parser/cbr/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C927"/>
+  <dimension ref="A1:C928"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -10589,6 +10589,17 @@
       </c>
       <c r="C927">
         <v>83.2454</v>
+      </c>
+    </row>
+    <row r="928" spans="1:3">
+      <c r="A928" s="2">
+        <v>46298</v>
+      </c>
+      <c r="B928">
+        <v>1</v>
+      </c>
+      <c r="C928">
+        <v>83.48390000000001</v>
       </c>
     </row>
   </sheetData>
@@ -10598,7 +10609,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C927"/>
+  <dimension ref="A1:C928"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -20796,6 +20807,17 @@
       </c>
       <c r="C927">
         <v>94.5252</v>
+      </c>
+    </row>
+    <row r="928" spans="1:3">
+      <c r="A928" s="2">
+        <v>46298</v>
+      </c>
+      <c r="B928">
+        <v>1</v>
+      </c>
+      <c r="C928">
+        <v>94.3201</v>
       </c>
     </row>
   </sheetData>
@@ -20805,7 +20827,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C927"/>
+  <dimension ref="A1:C928"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -31003,6 +31025,17 @@
       </c>
       <c r="C927">
         <v>57.8472</v>
+      </c>
+    </row>
+    <row r="928" spans="1:3">
+      <c r="A928" s="2">
+        <v>46298</v>
+      </c>
+      <c r="B928">
+        <v>1</v>
+      </c>
+      <c r="C928">
+        <v>57.8794</v>
       </c>
     </row>
   </sheetData>
@@ -31012,7 +31045,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C927"/>
+  <dimension ref="A1:C928"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -41210,6 +41243,17 @@
       </c>
       <c r="C927">
         <v>12.4028</v>
+      </c>
+    </row>
+    <row r="928" spans="1:3">
+      <c r="A928" s="2">
+        <v>46298</v>
+      </c>
+      <c r="B928">
+        <v>1</v>
+      </c>
+      <c r="C928">
+        <v>12.4328</v>
       </c>
     </row>
   </sheetData>
@@ -41219,7 +41263,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C927"/>
+  <dimension ref="A1:C928"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -51417,6 +51461,17 @@
       </c>
       <c r="C927">
         <v>110.5915</v>
+      </c>
+    </row>
+    <row r="928" spans="1:3">
+      <c r="A928" s="2">
+        <v>46298</v>
+      </c>
+      <c r="B928">
+        <v>1</v>
+      </c>
+      <c r="C928">
+        <v>110.2989</v>
       </c>
     </row>
   </sheetData>
@@ -51426,7 +51481,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C927"/>
+  <dimension ref="A1:C928"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -61624,6 +61679,17 @@
       </c>
       <c r="C927">
         <v>18.8825</v>
+      </c>
+    </row>
+    <row r="928" spans="1:3">
+      <c r="A928" s="2">
+        <v>46298</v>
+      </c>
+      <c r="B928">
+        <v>100</v>
+      </c>
+      <c r="C928">
+        <v>18.8916</v>
       </c>
     </row>
   </sheetData>
@@ -61633,7 +61699,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C927"/>
+  <dimension ref="A1:C928"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -71831,6 +71897,17 @@
       </c>
       <c r="C927">
         <v>52.637</v>
+      </c>
+    </row>
+    <row r="928" spans="1:3">
+      <c r="A928" s="2">
+        <v>46298</v>
+      </c>
+      <c r="B928">
+        <v>100</v>
+      </c>
+      <c r="C928">
+        <v>52.8112</v>
       </c>
     </row>
   </sheetData>
@@ -71840,7 +71917,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C927"/>
+  <dimension ref="A1:C928"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -82040,6 +82117,17 @@
         <v>99.6593</v>
       </c>
     </row>
+    <row r="928" spans="1:3">
+      <c r="A928" s="2">
+        <v>46298</v>
+      </c>
+      <c r="B928">
+        <v>1</v>
+      </c>
+      <c r="C928">
+        <v>100.7894</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/cbr/data/cb_currency.xlsx
+++ b/LME/parser/cbr/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C928"/>
+  <dimension ref="A1:C929"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -10600,6 +10600,17 @@
       </c>
       <c r="C928">
         <v>83.48390000000001</v>
+      </c>
+    </row>
+    <row r="929" spans="1:3">
+      <c r="A929" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B929">
+        <v>1</v>
+      </c>
+      <c r="C929">
+        <v>84.93089999999999</v>
       </c>
     </row>
   </sheetData>
@@ -10609,7 +10620,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C928"/>
+  <dimension ref="A1:C929"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -20818,6 +20829,17 @@
       </c>
       <c r="C928">
         <v>94.3201</v>
+      </c>
+    </row>
+    <row r="929" spans="1:3">
+      <c r="A929" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B929">
+        <v>1</v>
+      </c>
+      <c r="C929">
+        <v>95.3349</v>
       </c>
     </row>
   </sheetData>
@@ -20827,7 +20849,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C928"/>
+  <dimension ref="A1:C929"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -31036,6 +31058,17 @@
       </c>
       <c r="C928">
         <v>57.8794</v>
+      </c>
+    </row>
+    <row r="929" spans="1:3">
+      <c r="A929" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B929">
+        <v>1</v>
+      </c>
+      <c r="C929">
+        <v>58.8826</v>
       </c>
     </row>
   </sheetData>
@@ -31045,7 +31078,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C928"/>
+  <dimension ref="A1:C929"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -41254,6 +41287,17 @@
       </c>
       <c r="C928">
         <v>12.4328</v>
+      </c>
+    </row>
+    <row r="929" spans="1:3">
+      <c r="A929" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B929">
+        <v>1</v>
+      </c>
+      <c r="C929">
+        <v>12.6491</v>
       </c>
     </row>
   </sheetData>
@@ -41263,7 +41307,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C928"/>
+  <dimension ref="A1:C929"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -51472,6 +51516,17 @@
       </c>
       <c r="C928">
         <v>110.2989</v>
+      </c>
+    </row>
+    <row r="929" spans="1:3">
+      <c r="A929" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B929">
+        <v>1</v>
+      </c>
+      <c r="C929">
+        <v>112.5249</v>
       </c>
     </row>
   </sheetData>
@@ -51481,7 +51536,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C928"/>
+  <dimension ref="A1:C929"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -61690,6 +61745,17 @@
       </c>
       <c r="C928">
         <v>18.8916</v>
+      </c>
+    </row>
+    <row r="929" spans="1:3">
+      <c r="A929" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B929">
+        <v>100</v>
+      </c>
+      <c r="C929">
+        <v>18.9692</v>
       </c>
     </row>
   </sheetData>
@@ -61699,7 +61765,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C928"/>
+  <dimension ref="A1:C929"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -71908,6 +71974,17 @@
       </c>
       <c r="C928">
         <v>52.8112</v>
+      </c>
+    </row>
+    <row r="929" spans="1:3">
+      <c r="A929" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B929">
+        <v>100</v>
+      </c>
+      <c r="C929">
+        <v>53.8219</v>
       </c>
     </row>
   </sheetData>
@@ -71917,7 +71994,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C928"/>
+  <dimension ref="A1:C929"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -82128,6 +82205,17 @@
         <v>100.7894</v>
       </c>
     </row>
+    <row r="929" spans="1:3">
+      <c r="A929" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B929">
+        <v>1</v>
+      </c>
+      <c r="C929">
+        <v>102.4004</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/cbr/data/cb_currency.xlsx
+++ b/LME/parser/cbr/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C929"/>
+  <dimension ref="A1:C930"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -10611,6 +10611,17 @@
       </c>
       <c r="C929">
         <v>84.93089999999999</v>
+      </c>
+    </row>
+    <row r="930" spans="1:3">
+      <c r="A930" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B930">
+        <v>1</v>
+      </c>
+      <c r="C930">
+        <v>85.7116</v>
       </c>
     </row>
   </sheetData>
@@ -10620,7 +10631,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C929"/>
+  <dimension ref="A1:C930"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -20840,6 +20851,17 @@
       </c>
       <c r="C929">
         <v>95.3349</v>
+      </c>
+    </row>
+    <row r="930" spans="1:3">
+      <c r="A930" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B930">
+        <v>1</v>
+      </c>
+      <c r="C930">
+        <v>96.0313</v>
       </c>
     </row>
   </sheetData>
@@ -20849,7 +20871,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C929"/>
+  <dimension ref="A1:C930"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -31069,6 +31091,17 @@
       </c>
       <c r="C929">
         <v>58.8826</v>
+      </c>
+    </row>
+    <row r="930" spans="1:3">
+      <c r="A930" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B930">
+        <v>1</v>
+      </c>
+      <c r="C930">
+        <v>59.741</v>
       </c>
     </row>
   </sheetData>
@@ -31078,7 +31111,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C929"/>
+  <dimension ref="A1:C930"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -41298,6 +41331,17 @@
       </c>
       <c r="C929">
         <v>12.6491</v>
+      </c>
+    </row>
+    <row r="930" spans="1:3">
+      <c r="A930" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B930">
+        <v>1</v>
+      </c>
+      <c r="C930">
+        <v>12.7984</v>
       </c>
     </row>
   </sheetData>
@@ -41307,7 +41351,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C929"/>
+  <dimension ref="A1:C930"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -51527,6 +51571,17 @@
       </c>
       <c r="C929">
         <v>112.5249</v>
+      </c>
+    </row>
+    <row r="930" spans="1:3">
+      <c r="A930" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B930">
+        <v>1</v>
+      </c>
+      <c r="C930">
+        <v>113.3193</v>
       </c>
     </row>
   </sheetData>
@@ -51536,7 +51591,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C929"/>
+  <dimension ref="A1:C930"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -61756,6 +61811,17 @@
       </c>
       <c r="C929">
         <v>18.9692</v>
+      </c>
+    </row>
+    <row r="930" spans="1:3">
+      <c r="A930" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B930">
+        <v>100</v>
+      </c>
+      <c r="C930">
+        <v>18.8385</v>
       </c>
     </row>
   </sheetData>
@@ -61765,7 +61831,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C929"/>
+  <dimension ref="A1:C930"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -71985,6 +72051,17 @@
       </c>
       <c r="C929">
         <v>53.8219</v>
+      </c>
+    </row>
+    <row r="930" spans="1:3">
+      <c r="A930" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B930">
+        <v>100</v>
+      </c>
+      <c r="C930">
+        <v>54.2753</v>
       </c>
     </row>
   </sheetData>
@@ -71994,7 +72071,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C929"/>
+  <dimension ref="A1:C930"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -82216,6 +82293,17 @@
         <v>102.4004</v>
       </c>
     </row>
+    <row r="930" spans="1:3">
+      <c r="A930" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B930">
+        <v>1</v>
+      </c>
+      <c r="C930">
+        <v>103.0188</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/cbr/data/cb_currency.xlsx
+++ b/LME/parser/cbr/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C930"/>
+  <dimension ref="A1:C931"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -10622,6 +10622,17 @@
       </c>
       <c r="C930">
         <v>85.7116</v>
+      </c>
+    </row>
+    <row r="931" spans="1:3">
+      <c r="A931" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B931">
+        <v>1</v>
+      </c>
+      <c r="C931">
+        <v>85.4811</v>
       </c>
     </row>
   </sheetData>
@@ -10631,7 +10642,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C930"/>
+  <dimension ref="A1:C931"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -20862,6 +20873,17 @@
       </c>
       <c r="C930">
         <v>96.0313</v>
+      </c>
+    </row>
+    <row r="931" spans="1:3">
+      <c r="A931" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B931">
+        <v>1</v>
+      </c>
+      <c r="C931">
+        <v>96.3287</v>
       </c>
     </row>
   </sheetData>
@@ -20871,7 +20893,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C930"/>
+  <dimension ref="A1:C931"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -31102,6 +31124,17 @@
       </c>
       <c r="C930">
         <v>59.741</v>
+      </c>
+    </row>
+    <row r="931" spans="1:3">
+      <c r="A931" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B931">
+        <v>1</v>
+      </c>
+      <c r="C931">
+        <v>59.5803</v>
       </c>
     </row>
   </sheetData>
@@ -31111,7 +31144,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C930"/>
+  <dimension ref="A1:C931"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -41342,6 +41375,17 @@
       </c>
       <c r="C930">
         <v>12.7984</v>
+      </c>
+    </row>
+    <row r="931" spans="1:3">
+      <c r="A931" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B931">
+        <v>1</v>
+      </c>
+      <c r="C931">
+        <v>12.7516</v>
       </c>
     </row>
   </sheetData>
@@ -41351,7 +41395,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C930"/>
+  <dimension ref="A1:C931"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -51582,6 +51626,17 @@
       </c>
       <c r="C930">
         <v>113.3193</v>
+      </c>
+    </row>
+    <row r="931" spans="1:3">
+      <c r="A931" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B931">
+        <v>1</v>
+      </c>
+      <c r="C931">
+        <v>113.5104</v>
       </c>
     </row>
   </sheetData>
@@ -51591,7 +51646,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C930"/>
+  <dimension ref="A1:C931"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -61822,6 +61877,17 @@
       </c>
       <c r="C930">
         <v>18.8385</v>
+      </c>
+    </row>
+    <row r="931" spans="1:3">
+      <c r="A931" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B931">
+        <v>100</v>
+      </c>
+      <c r="C931">
+        <v>18.843</v>
       </c>
     </row>
   </sheetData>
@@ -61831,7 +61897,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C930"/>
+  <dimension ref="A1:C931"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -72062,6 +72128,17 @@
       </c>
       <c r="C930">
         <v>54.2753</v>
+      </c>
+    </row>
+    <row r="931" spans="1:3">
+      <c r="A931" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B931">
+        <v>100</v>
+      </c>
+      <c r="C931">
+        <v>53.9449</v>
       </c>
     </row>
   </sheetData>
@@ -72071,7 +72148,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C930"/>
+  <dimension ref="A1:C931"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -82304,6 +82381,17 @@
         <v>103.0188</v>
       </c>
     </row>
+    <row r="931" spans="1:3">
+      <c r="A931" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B931">
+        <v>1</v>
+      </c>
+      <c r="C931">
+        <v>102.5937</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/cbr/data/cb_currency.xlsx
+++ b/LME/parser/cbr/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C931"/>
+  <dimension ref="A1:C932"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -10633,6 +10633,17 @@
       </c>
       <c r="C931">
         <v>85.4811</v>
+      </c>
+    </row>
+    <row r="932" spans="1:3">
+      <c r="A932" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B932">
+        <v>1</v>
+      </c>
+      <c r="C932">
+        <v>85.4173</v>
       </c>
     </row>
   </sheetData>
@@ -10642,7 +10653,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C931"/>
+  <dimension ref="A1:C932"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -20884,6 +20895,17 @@
       </c>
       <c r="C931">
         <v>96.3287</v>
+      </c>
+    </row>
+    <row r="932" spans="1:3">
+      <c r="A932" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B932">
+        <v>1</v>
+      </c>
+      <c r="C932">
+        <v>95.4709</v>
       </c>
     </row>
   </sheetData>
@@ -20893,7 +20915,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C931"/>
+  <dimension ref="A1:C932"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -31135,6 +31157,17 @@
       </c>
       <c r="C931">
         <v>59.5803</v>
+      </c>
+    </row>
+    <row r="932" spans="1:3">
+      <c r="A932" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B932">
+        <v>1</v>
+      </c>
+      <c r="C932">
+        <v>59.4163</v>
       </c>
     </row>
   </sheetData>
@@ -31144,7 +31177,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C931"/>
+  <dimension ref="A1:C932"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -41386,6 +41419,17 @@
       </c>
       <c r="C931">
         <v>12.7516</v>
+      </c>
+    </row>
+    <row r="932" spans="1:3">
+      <c r="A932" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B932">
+        <v>1</v>
+      </c>
+      <c r="C932">
+        <v>12.732</v>
       </c>
     </row>
   </sheetData>
@@ -41395,7 +41439,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C931"/>
+  <dimension ref="A1:C932"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -51637,6 +51681,17 @@
       </c>
       <c r="C931">
         <v>113.5104</v>
+      </c>
+    </row>
+    <row r="932" spans="1:3">
+      <c r="A932" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B932">
+        <v>1</v>
+      </c>
+      <c r="C932">
+        <v>112.9217</v>
       </c>
     </row>
   </sheetData>
@@ -51646,7 +51701,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C931"/>
+  <dimension ref="A1:C932"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -61888,6 +61943,17 @@
       </c>
       <c r="C931">
         <v>18.843</v>
+      </c>
+    </row>
+    <row r="932" spans="1:3">
+      <c r="A932" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B932">
+        <v>100</v>
+      </c>
+      <c r="C932">
+        <v>19.103</v>
       </c>
     </row>
   </sheetData>
@@ -61897,7 +61963,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C931"/>
+  <dimension ref="A1:C932"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -72139,6 +72205,17 @@
       </c>
       <c r="C931">
         <v>53.9449</v>
+      </c>
+    </row>
+    <row r="932" spans="1:3">
+      <c r="A932" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B932">
+        <v>100</v>
+      </c>
+      <c r="C932">
+        <v>54.1061</v>
       </c>
     </row>
   </sheetData>
@@ -72148,7 +72225,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C931"/>
+  <dimension ref="A1:C932"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -82392,6 +82469,17 @@
         <v>102.5937</v>
       </c>
     </row>
+    <row r="932" spans="1:3">
+      <c r="A932" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B932">
+        <v>1</v>
+      </c>
+      <c r="C932">
+        <v>102.4434</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/cbr/data/cb_currency.xlsx
+++ b/LME/parser/cbr/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C932"/>
+  <dimension ref="A1:C933"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -10644,6 +10644,17 @@
       </c>
       <c r="C932">
         <v>85.4173</v>
+      </c>
+    </row>
+    <row r="933" spans="1:3">
+      <c r="A933" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B933">
+        <v>1</v>
+      </c>
+      <c r="C933">
+        <v>84.90479999999999</v>
       </c>
     </row>
   </sheetData>
@@ -10653,7 +10664,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C932"/>
+  <dimension ref="A1:C933"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -20906,6 +20917,17 @@
       </c>
       <c r="C932">
         <v>95.4709</v>
+      </c>
+    </row>
+    <row r="933" spans="1:3">
+      <c r="A933" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B933">
+        <v>1</v>
+      </c>
+      <c r="C933">
+        <v>94.97450000000001</v>
       </c>
     </row>
   </sheetData>
@@ -20915,7 +20937,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C932"/>
+  <dimension ref="A1:C933"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -31168,6 +31190,17 @@
       </c>
       <c r="C932">
         <v>59.4163</v>
+      </c>
+    </row>
+    <row r="933" spans="1:3">
+      <c r="A933" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B933">
+        <v>1</v>
+      </c>
+      <c r="C933">
+        <v>59.2551</v>
       </c>
     </row>
   </sheetData>
@@ -31177,7 +31210,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C932"/>
+  <dimension ref="A1:C933"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -41430,6 +41463,17 @@
       </c>
       <c r="C932">
         <v>12.732</v>
+      </c>
+    </row>
+    <row r="933" spans="1:3">
+      <c r="A933" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B933">
+        <v>1</v>
+      </c>
+      <c r="C933">
+        <v>12.6739</v>
       </c>
     </row>
   </sheetData>
@@ -41439,7 +41483,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C932"/>
+  <dimension ref="A1:C933"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -51692,6 +51736,17 @@
       </c>
       <c r="C932">
         <v>112.9217</v>
+      </c>
+    </row>
+    <row r="933" spans="1:3">
+      <c r="A933" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B933">
+        <v>1</v>
+      </c>
+      <c r="C933">
+        <v>112.2951</v>
       </c>
     </row>
   </sheetData>
@@ -51701,7 +51756,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C932"/>
+  <dimension ref="A1:C933"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -61954,6 +62009,17 @@
       </c>
       <c r="C932">
         <v>19.103</v>
+      </c>
+    </row>
+    <row r="933" spans="1:3">
+      <c r="A933" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B933">
+        <v>100</v>
+      </c>
+      <c r="C933">
+        <v>18.9123</v>
       </c>
     </row>
   </sheetData>
@@ -61963,7 +62029,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C932"/>
+  <dimension ref="A1:C933"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -72216,6 +72282,17 @@
       </c>
       <c r="C932">
         <v>54.1061</v>
+      </c>
+    </row>
+    <row r="933" spans="1:3">
+      <c r="A933" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B933">
+        <v>100</v>
+      </c>
+      <c r="C933">
+        <v>53.7032</v>
       </c>
     </row>
   </sheetData>
@@ -72225,7 +72302,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C932"/>
+  <dimension ref="A1:C933"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -82480,6 +82557,17 @@
         <v>102.4434</v>
       </c>
     </row>
+    <row r="933" spans="1:3">
+      <c r="A933" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B933">
+        <v>1</v>
+      </c>
+      <c r="C933">
+        <v>102.1595</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/cbr/data/cb_currency.xlsx
+++ b/LME/parser/cbr/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C933"/>
+  <dimension ref="A1:C934"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -10655,6 +10655,17 @@
       </c>
       <c r="C933">
         <v>84.90479999999999</v>
+      </c>
+    </row>
+    <row r="934" spans="1:3">
+      <c r="A934" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B934">
+        <v>1</v>
+      </c>
+      <c r="C934">
+        <v>83.9153</v>
       </c>
     </row>
   </sheetData>
@@ -10664,7 +10675,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C933"/>
+  <dimension ref="A1:C934"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -20928,6 +20939,17 @@
       </c>
       <c r="C933">
         <v>94.97450000000001</v>
+      </c>
+    </row>
+    <row r="934" spans="1:3">
+      <c r="A934" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B934">
+        <v>1</v>
+      </c>
+      <c r="C934">
+        <v>94.0355</v>
       </c>
     </row>
   </sheetData>
@@ -20937,7 +20959,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C933"/>
+  <dimension ref="A1:C934"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -31201,6 +31223,17 @@
       </c>
       <c r="C933">
         <v>59.2551</v>
+      </c>
+    </row>
+    <row r="934" spans="1:3">
+      <c r="A934" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B934">
+        <v>1</v>
+      </c>
+      <c r="C934">
+        <v>58.5645</v>
       </c>
     </row>
   </sheetData>
@@ -31210,7 +31243,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C933"/>
+  <dimension ref="A1:C934"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -41474,6 +41507,17 @@
       </c>
       <c r="C933">
         <v>12.6739</v>
+      </c>
+    </row>
+    <row r="934" spans="1:3">
+      <c r="A934" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B934">
+        <v>1</v>
+      </c>
+      <c r="C934">
+        <v>12.536</v>
       </c>
     </row>
   </sheetData>
@@ -41483,7 +41527,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C933"/>
+  <dimension ref="A1:C934"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -51747,6 +51791,17 @@
       </c>
       <c r="C933">
         <v>112.2951</v>
+      </c>
+    </row>
+    <row r="934" spans="1:3">
+      <c r="A934" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B934">
+        <v>1</v>
+      </c>
+      <c r="C934">
+        <v>110.978</v>
       </c>
     </row>
   </sheetData>
@@ -51756,7 +51811,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C933"/>
+  <dimension ref="A1:C934"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -62020,6 +62075,17 @@
       </c>
       <c r="C933">
         <v>18.9123</v>
+      </c>
+    </row>
+    <row r="934" spans="1:3">
+      <c r="A934" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B934">
+        <v>100</v>
+      </c>
+      <c r="C934">
+        <v>18.4864</v>
       </c>
     </row>
   </sheetData>
@@ -62029,7 +62095,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C933"/>
+  <dimension ref="A1:C934"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -72293,6 +72359,17 @@
       </c>
       <c r="C933">
         <v>53.7032</v>
+      </c>
+    </row>
+    <row r="934" spans="1:3">
+      <c r="A934" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B934">
+        <v>100</v>
+      </c>
+      <c r="C934">
+        <v>53.0774</v>
       </c>
     </row>
   </sheetData>
@@ -72302,7 +72379,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C933"/>
+  <dimension ref="A1:C934"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -82568,6 +82645,17 @@
         <v>102.1595</v>
       </c>
     </row>
+    <row r="934" spans="1:3">
+      <c r="A934" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B934">
+        <v>1</v>
+      </c>
+      <c r="C934">
+        <v>100.8234</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/cbr/data/cb_currency.xlsx
+++ b/LME/parser/cbr/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C934"/>
+  <dimension ref="A1:C935"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -10666,6 +10666,17 @@
       </c>
       <c r="C934">
         <v>83.9153</v>
+      </c>
+    </row>
+    <row r="935" spans="1:3">
+      <c r="A935" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B935">
+        <v>1</v>
+      </c>
+      <c r="C935">
+        <v>83.86750000000001</v>
       </c>
     </row>
   </sheetData>
@@ -10675,7 +10686,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C934"/>
+  <dimension ref="A1:C935"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -20950,6 +20961,17 @@
       </c>
       <c r="C934">
         <v>94.0355</v>
+      </c>
+    </row>
+    <row r="935" spans="1:3">
+      <c r="A935" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B935">
+        <v>1</v>
+      </c>
+      <c r="C935">
+        <v>93.7723</v>
       </c>
     </row>
   </sheetData>
@@ -20959,7 +20981,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C934"/>
+  <dimension ref="A1:C935"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -31234,6 +31256,17 @@
       </c>
       <c r="C934">
         <v>58.5645</v>
+      </c>
+    </row>
+    <row r="935" spans="1:3">
+      <c r="A935" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B935">
+        <v>1</v>
+      </c>
+      <c r="C935">
+        <v>58.3802</v>
       </c>
     </row>
   </sheetData>
@@ -31243,7 +31276,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C934"/>
+  <dimension ref="A1:C935"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -41518,6 +41551,17 @@
       </c>
       <c r="C934">
         <v>12.536</v>
+      </c>
+    </row>
+    <row r="935" spans="1:3">
+      <c r="A935" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B935">
+        <v>1</v>
+      </c>
+      <c r="C935">
+        <v>12.5028</v>
       </c>
     </row>
   </sheetData>
@@ -41527,7 +41571,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C934"/>
+  <dimension ref="A1:C935"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -51802,6 +51846,17 @@
       </c>
       <c r="C934">
         <v>110.978</v>
+      </c>
+    </row>
+    <row r="935" spans="1:3">
+      <c r="A935" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B935">
+        <v>1</v>
+      </c>
+      <c r="C935">
+        <v>110.8728</v>
       </c>
     </row>
   </sheetData>
@@ -51811,7 +51866,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C934"/>
+  <dimension ref="A1:C935"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -62086,6 +62141,17 @@
       </c>
       <c r="C934">
         <v>18.4864</v>
+      </c>
+    </row>
+    <row r="935" spans="1:3">
+      <c r="A935" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B935">
+        <v>100</v>
+      </c>
+      <c r="C935">
+        <v>18.5831</v>
       </c>
     </row>
   </sheetData>
@@ -62095,7 +62161,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C934"/>
+  <dimension ref="A1:C935"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -72370,6 +72436,17 @@
       </c>
       <c r="C934">
         <v>53.0774</v>
+      </c>
+    </row>
+    <row r="935" spans="1:3">
+      <c r="A935" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B935">
+        <v>100</v>
+      </c>
+      <c r="C935">
+        <v>52.9166</v>
       </c>
     </row>
   </sheetData>
@@ -72379,7 +72456,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C934"/>
+  <dimension ref="A1:C935"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -82656,6 +82733,17 @@
         <v>100.8234</v>
       </c>
     </row>
+    <row r="935" spans="1:3">
+      <c r="A935" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B935">
+        <v>1</v>
+      </c>
+      <c r="C935">
+        <v>100.6934</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/cbr/data/cb_currency.xlsx
+++ b/LME/parser/cbr/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C935"/>
+  <dimension ref="A1:C936"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -10677,6 +10677,17 @@
       </c>
       <c r="C935">
         <v>83.86750000000001</v>
+      </c>
+    </row>
+    <row r="936" spans="1:3">
+      <c r="A936" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B936">
+        <v>1</v>
+      </c>
+      <c r="C936">
+        <v>83.94970000000001</v>
       </c>
     </row>
   </sheetData>
@@ -10686,7 +10697,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C935"/>
+  <dimension ref="A1:C936"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -20972,6 +20983,17 @@
       </c>
       <c r="C935">
         <v>93.7723</v>
+      </c>
+    </row>
+    <row r="936" spans="1:3">
+      <c r="A936" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B936">
+        <v>1</v>
+      </c>
+      <c r="C936">
+        <v>93.9229</v>
       </c>
     </row>
   </sheetData>
@@ -20981,7 +21003,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C935"/>
+  <dimension ref="A1:C936"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -31267,6 +31289,17 @@
       </c>
       <c r="C935">
         <v>58.3802</v>
+      </c>
+    </row>
+    <row r="936" spans="1:3">
+      <c r="A936" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B936">
+        <v>1</v>
+      </c>
+      <c r="C936">
+        <v>58.7816</v>
       </c>
     </row>
   </sheetData>
@@ -31276,7 +31309,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C935"/>
+  <dimension ref="A1:C936"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -41562,6 +41595,17 @@
       </c>
       <c r="C935">
         <v>12.5028</v>
+      </c>
+    </row>
+    <row r="936" spans="1:3">
+      <c r="A936" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B936">
+        <v>1</v>
+      </c>
+      <c r="C936">
+        <v>12.5358</v>
       </c>
     </row>
   </sheetData>
@@ -41571,7 +41615,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C935"/>
+  <dimension ref="A1:C936"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -51857,6 +51901,17 @@
       </c>
       <c r="C935">
         <v>110.8728</v>
+      </c>
+    </row>
+    <row r="936" spans="1:3">
+      <c r="A936" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B936">
+        <v>1</v>
+      </c>
+      <c r="C936">
+        <v>111.225</v>
       </c>
     </row>
   </sheetData>
@@ -51866,7 +51921,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C935"/>
+  <dimension ref="A1:C936"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -62152,6 +62207,17 @@
       </c>
       <c r="C935">
         <v>18.5831</v>
+      </c>
+    </row>
+    <row r="936" spans="1:3">
+      <c r="A936" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B936">
+        <v>100</v>
+      </c>
+      <c r="C936">
+        <v>18.72</v>
       </c>
     </row>
   </sheetData>
@@ -62161,7 +62227,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C935"/>
+  <dimension ref="A1:C936"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -72447,6 +72513,17 @@
       </c>
       <c r="C935">
         <v>52.9166</v>
+      </c>
+    </row>
+    <row r="936" spans="1:3">
+      <c r="A936" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B936">
+        <v>100</v>
+      </c>
+      <c r="C936">
+        <v>52.9852</v>
       </c>
     </row>
   </sheetData>
@@ -72456,7 +72533,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C935"/>
+  <dimension ref="A1:C936"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -82744,6 +82821,17 @@
         <v>100.6934</v>
       </c>
     </row>
+    <row r="936" spans="1:3">
+      <c r="A936" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B936">
+        <v>1</v>
+      </c>
+      <c r="C936">
+        <v>100.7195</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/cbr/data/cb_currency.xlsx
+++ b/LME/parser/cbr/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C936"/>
+  <dimension ref="A1:C937"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -10688,6 +10688,17 @@
       </c>
       <c r="C936">
         <v>83.94970000000001</v>
+      </c>
+    </row>
+    <row r="937" spans="1:3">
+      <c r="A937" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B937">
+        <v>1</v>
+      </c>
+      <c r="C937">
+        <v>83.76000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -10697,7 +10708,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C936"/>
+  <dimension ref="A1:C937"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -20994,6 +21005,17 @@
       </c>
       <c r="C936">
         <v>93.9229</v>
+      </c>
+    </row>
+    <row r="937" spans="1:3">
+      <c r="A937" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B937">
+        <v>1</v>
+      </c>
+      <c r="C937">
+        <v>93.7693</v>
       </c>
     </row>
   </sheetData>
@@ -21003,7 +21025,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C936"/>
+  <dimension ref="A1:C937"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -31300,6 +31322,17 @@
       </c>
       <c r="C936">
         <v>58.7816</v>
+      </c>
+    </row>
+    <row r="937" spans="1:3">
+      <c r="A937" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B937">
+        <v>1</v>
+      </c>
+      <c r="C937">
+        <v>58.2551</v>
       </c>
     </row>
   </sheetData>
@@ -31309,7 +31342,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C936"/>
+  <dimension ref="A1:C937"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -41606,6 +41639,17 @@
       </c>
       <c r="C936">
         <v>12.5358</v>
+      </c>
+    </row>
+    <row r="937" spans="1:3">
+      <c r="A937" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B937">
+        <v>1</v>
+      </c>
+      <c r="C937">
+        <v>12.4991</v>
       </c>
     </row>
   </sheetData>
@@ -41615,7 +41659,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C936"/>
+  <dimension ref="A1:C937"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -51912,6 +51956,17 @@
       </c>
       <c r="C936">
         <v>111.225</v>
+      </c>
+    </row>
+    <row r="937" spans="1:3">
+      <c r="A937" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B937">
+        <v>1</v>
+      </c>
+      <c r="C937">
+        <v>110.2282</v>
       </c>
     </row>
   </sheetData>
@@ -51921,7 +51976,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C936"/>
+  <dimension ref="A1:C937"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -62218,6 +62273,17 @@
       </c>
       <c r="C936">
         <v>18.72</v>
+      </c>
+    </row>
+    <row r="937" spans="1:3">
+      <c r="A937" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B937">
+        <v>100</v>
+      </c>
+      <c r="C937">
+        <v>18.5877</v>
       </c>
     </row>
   </sheetData>
@@ -62227,7 +62293,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C936"/>
+  <dimension ref="A1:C937"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -72524,6 +72590,17 @@
       </c>
       <c r="C936">
         <v>52.9852</v>
+      </c>
+    </row>
+    <row r="937" spans="1:3">
+      <c r="A937" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B937">
+        <v>100</v>
+      </c>
+      <c r="C937">
+        <v>53.0328</v>
       </c>
     </row>
   </sheetData>
@@ -72533,7 +72610,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C936"/>
+  <dimension ref="A1:C937"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -82832,6 +82909,17 @@
         <v>100.7195</v>
       </c>
     </row>
+    <row r="937" spans="1:3">
+      <c r="A937" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B937">
+        <v>1</v>
+      </c>
+      <c r="C937">
+        <v>100.9522</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/cbr/data/cb_currency.xlsx
+++ b/LME/parser/cbr/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C937"/>
+  <dimension ref="A1:C938"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -10699,6 +10699,17 @@
       </c>
       <c r="C937">
         <v>83.76000000000001</v>
+      </c>
+    </row>
+    <row r="938" spans="1:3">
+      <c r="A938" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B938">
+        <v>1</v>
+      </c>
+      <c r="C938">
+        <v>83.6177</v>
       </c>
     </row>
   </sheetData>
@@ -10708,7 +10719,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C937"/>
+  <dimension ref="A1:C938"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -21016,6 +21027,17 @@
       </c>
       <c r="C937">
         <v>93.7693</v>
+      </c>
+    </row>
+    <row r="938" spans="1:3">
+      <c r="A938" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B938">
+        <v>1</v>
+      </c>
+      <c r="C938">
+        <v>93.7187</v>
       </c>
     </row>
   </sheetData>
@@ -21025,7 +21047,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C937"/>
+  <dimension ref="A1:C938"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -31333,6 +31355,17 @@
       </c>
       <c r="C937">
         <v>58.2551</v>
+      </c>
+    </row>
+    <row r="938" spans="1:3">
+      <c r="A938" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B938">
+        <v>1</v>
+      </c>
+      <c r="C938">
+        <v>58.0892</v>
       </c>
     </row>
   </sheetData>
@@ -31342,7 +31375,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C937"/>
+  <dimension ref="A1:C938"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -41650,6 +41683,17 @@
       </c>
       <c r="C937">
         <v>12.4991</v>
+      </c>
+    </row>
+    <row r="938" spans="1:3">
+      <c r="A938" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B938">
+        <v>1</v>
+      </c>
+      <c r="C938">
+        <v>12.495</v>
       </c>
     </row>
   </sheetData>
@@ -41659,7 +41703,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C937"/>
+  <dimension ref="A1:C938"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -51967,6 +52011,17 @@
       </c>
       <c r="C937">
         <v>110.2282</v>
+      </c>
+    </row>
+    <row r="938" spans="1:3">
+      <c r="A938" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B938">
+        <v>1</v>
+      </c>
+      <c r="C938">
+        <v>110.8185</v>
       </c>
     </row>
   </sheetData>
@@ -51976,7 +52031,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C937"/>
+  <dimension ref="A1:C938"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -62284,6 +62339,17 @@
       </c>
       <c r="C937">
         <v>18.5877</v>
+      </c>
+    </row>
+    <row r="938" spans="1:3">
+      <c r="A938" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B938">
+        <v>100</v>
+      </c>
+      <c r="C938">
+        <v>18.4123</v>
       </c>
     </row>
   </sheetData>
@@ -62293,7 +62359,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C937"/>
+  <dimension ref="A1:C938"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -72601,6 +72667,17 @@
       </c>
       <c r="C937">
         <v>53.0328</v>
+      </c>
+    </row>
+    <row r="938" spans="1:3">
+      <c r="A938" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B938">
+        <v>100</v>
+      </c>
+      <c r="C938">
+        <v>52.8691</v>
       </c>
     </row>
   </sheetData>
@@ -72610,7 +72687,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C937"/>
+  <dimension ref="A1:C938"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -82920,6 +82997,17 @@
         <v>100.9522</v>
       </c>
     </row>
+    <row r="938" spans="1:3">
+      <c r="A938" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B938">
+        <v>1</v>
+      </c>
+      <c r="C938">
+        <v>101.4163</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/cbr/data/cb_currency.xlsx
+++ b/LME/parser/cbr/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C938"/>
+  <dimension ref="A1:C939"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -10710,6 +10710,17 @@
       </c>
       <c r="C938">
         <v>83.6177</v>
+      </c>
+    </row>
+    <row r="939" spans="1:3">
+      <c r="A939" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B939">
+        <v>1</v>
+      </c>
+      <c r="C939">
+        <v>82.85039999999999</v>
       </c>
     </row>
   </sheetData>
@@ -10719,7 +10730,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C938"/>
+  <dimension ref="A1:C939"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -21038,6 +21049,17 @@
       </c>
       <c r="C938">
         <v>93.7187</v>
+      </c>
+    </row>
+    <row r="939" spans="1:3">
+      <c r="A939" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B939">
+        <v>1</v>
+      </c>
+      <c r="C939">
+        <v>93.2316</v>
       </c>
     </row>
   </sheetData>
@@ -21047,7 +21069,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C938"/>
+  <dimension ref="A1:C939"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -31366,6 +31388,17 @@
       </c>
       <c r="C938">
         <v>58.0892</v>
+      </c>
+    </row>
+    <row r="939" spans="1:3">
+      <c r="A939" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B939">
+        <v>1</v>
+      </c>
+      <c r="C939">
+        <v>57.7882</v>
       </c>
     </row>
   </sheetData>
@@ -31375,7 +31408,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C938"/>
+  <dimension ref="A1:C939"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -41694,6 +41727,17 @@
       </c>
       <c r="C938">
         <v>12.495</v>
+      </c>
+    </row>
+    <row r="939" spans="1:3">
+      <c r="A939" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B939">
+        <v>1</v>
+      </c>
+      <c r="C939">
+        <v>12.3869</v>
       </c>
     </row>
   </sheetData>
@@ -41703,7 +41747,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C938"/>
+  <dimension ref="A1:C939"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -52022,6 +52066,17 @@
       </c>
       <c r="C938">
         <v>110.8185</v>
+      </c>
+    </row>
+    <row r="939" spans="1:3">
+      <c r="A939" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B939">
+        <v>1</v>
+      </c>
+      <c r="C939">
+        <v>110.6301</v>
       </c>
     </row>
   </sheetData>
@@ -52031,7 +52086,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C938"/>
+  <dimension ref="A1:C939"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -62350,6 +62405,17 @@
       </c>
       <c r="C938">
         <v>18.4123</v>
+      </c>
+    </row>
+    <row r="939" spans="1:3">
+      <c r="A939" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B939">
+        <v>100</v>
+      </c>
+      <c r="C939">
+        <v>18.3249</v>
       </c>
     </row>
   </sheetData>
@@ -62359,7 +62425,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C938"/>
+  <dimension ref="A1:C939"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -72678,6 +72744,17 @@
       </c>
       <c r="C938">
         <v>52.8691</v>
+      </c>
+    </row>
+    <row r="939" spans="1:3">
+      <c r="A939" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B939">
+        <v>100</v>
+      </c>
+      <c r="C939">
+        <v>52.4668</v>
       </c>
     </row>
   </sheetData>
@@ -72687,7 +72764,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C938"/>
+  <dimension ref="A1:C939"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -83008,6 +83085,17 @@
         <v>101.4163</v>
       </c>
     </row>
+    <row r="939" spans="1:3">
+      <c r="A939" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B939">
+        <v>1</v>
+      </c>
+      <c r="C939">
+        <v>100.4856</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/cbr/data/cb_currency.xlsx
+++ b/LME/parser/cbr/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C939"/>
+  <dimension ref="A1:C940"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -10721,6 +10721,17 @@
       </c>
       <c r="C939">
         <v>82.85039999999999</v>
+      </c>
+    </row>
+    <row r="940" spans="1:3">
+      <c r="A940" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B940">
+        <v>1</v>
+      </c>
+      <c r="C940">
+        <v>82.8879</v>
       </c>
     </row>
   </sheetData>
@@ -10730,7 +10741,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C939"/>
+  <dimension ref="A1:C940"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -21060,6 +21071,17 @@
       </c>
       <c r="C939">
         <v>93.2316</v>
+      </c>
+    </row>
+    <row r="940" spans="1:3">
+      <c r="A940" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B940">
+        <v>1</v>
+      </c>
+      <c r="C940">
+        <v>93.04170000000001</v>
       </c>
     </row>
   </sheetData>
@@ -21069,7 +21091,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C939"/>
+  <dimension ref="A1:C940"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -31399,6 +31421,17 @@
       </c>
       <c r="C939">
         <v>57.7882</v>
+      </c>
+    </row>
+    <row r="940" spans="1:3">
+      <c r="A940" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B940">
+        <v>1</v>
+      </c>
+      <c r="C940">
+        <v>57.8889</v>
       </c>
     </row>
   </sheetData>
@@ -31408,7 +31441,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C939"/>
+  <dimension ref="A1:C940"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -41738,6 +41771,17 @@
       </c>
       <c r="C939">
         <v>12.3869</v>
+      </c>
+    </row>
+    <row r="940" spans="1:3">
+      <c r="A940" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B940">
+        <v>1</v>
+      </c>
+      <c r="C940">
+        <v>12.3708</v>
       </c>
     </row>
   </sheetData>
@@ -41747,7 +41791,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C939"/>
+  <dimension ref="A1:C940"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -52077,6 +52121,17 @@
       </c>
       <c r="C939">
         <v>110.6301</v>
+      </c>
+    </row>
+    <row r="940" spans="1:3">
+      <c r="A940" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B940">
+        <v>1</v>
+      </c>
+      <c r="C940">
+        <v>110.3901</v>
       </c>
     </row>
   </sheetData>
@@ -52086,7 +52141,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C939"/>
+  <dimension ref="A1:C940"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -62416,6 +62471,17 @@
       </c>
       <c r="C939">
         <v>18.3249</v>
+      </c>
+    </row>
+    <row r="940" spans="1:3">
+      <c r="A940" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B940">
+        <v>100</v>
+      </c>
+      <c r="C940">
+        <v>18.3141</v>
       </c>
     </row>
   </sheetData>
@@ -62425,7 +62491,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C939"/>
+  <dimension ref="A1:C940"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -72755,6 +72821,17 @@
       </c>
       <c r="C939">
         <v>52.4668</v>
+      </c>
+    </row>
+    <row r="940" spans="1:3">
+      <c r="A940" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B940">
+        <v>100</v>
+      </c>
+      <c r="C940">
+        <v>52.2688</v>
       </c>
     </row>
   </sheetData>
@@ -72764,7 +72841,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C939"/>
+  <dimension ref="A1:C940"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -83096,6 +83173,17 @@
         <v>100.4856</v>
       </c>
     </row>
+    <row r="940" spans="1:3">
+      <c r="A940" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B940">
+        <v>1</v>
+      </c>
+      <c r="C940">
+        <v>100.5067</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/cbr/data/cb_currency.xlsx
+++ b/LME/parser/cbr/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C940"/>
+  <dimension ref="A1:C941"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -10732,6 +10732,17 @@
       </c>
       <c r="C940">
         <v>82.8879</v>
+      </c>
+    </row>
+    <row r="941" spans="1:3">
+      <c r="A941" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B941">
+        <v>1</v>
+      </c>
+      <c r="C941">
+        <v>81.9739</v>
       </c>
     </row>
   </sheetData>
@@ -10741,7 +10752,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C940"/>
+  <dimension ref="A1:C941"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -21082,6 +21093,17 @@
       </c>
       <c r="C940">
         <v>93.04170000000001</v>
+      </c>
+    </row>
+    <row r="941" spans="1:3">
+      <c r="A941" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B941">
+        <v>1</v>
+      </c>
+      <c r="C941">
+        <v>91.9337</v>
       </c>
     </row>
   </sheetData>
@@ -21091,7 +21113,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C940"/>
+  <dimension ref="A1:C941"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -31432,6 +31454,17 @@
       </c>
       <c r="C940">
         <v>57.8889</v>
+      </c>
+    </row>
+    <row r="941" spans="1:3">
+      <c r="A941" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B941">
+        <v>1</v>
+      </c>
+      <c r="C941">
+        <v>57.4637</v>
       </c>
     </row>
   </sheetData>
@@ -31441,7 +31474,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C940"/>
+  <dimension ref="A1:C941"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -41782,6 +41815,17 @@
       </c>
       <c r="C940">
         <v>12.3708</v>
+      </c>
+    </row>
+    <row r="941" spans="1:3">
+      <c r="A941" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B941">
+        <v>1</v>
+      </c>
+      <c r="C941">
+        <v>12.2806</v>
       </c>
     </row>
   </sheetData>
@@ -41791,7 +41835,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C940"/>
+  <dimension ref="A1:C941"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -52132,6 +52176,17 @@
       </c>
       <c r="C940">
         <v>110.3901</v>
+      </c>
+    </row>
+    <row r="941" spans="1:3">
+      <c r="A941" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B941">
+        <v>1</v>
+      </c>
+      <c r="C941">
+        <v>109.7385</v>
       </c>
     </row>
   </sheetData>
@@ -52141,7 +52196,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C940"/>
+  <dimension ref="A1:C941"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -62482,6 +62537,17 @@
       </c>
       <c r="C940">
         <v>18.3141</v>
+      </c>
+    </row>
+    <row r="941" spans="1:3">
+      <c r="A941" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B941">
+        <v>100</v>
+      </c>
+      <c r="C941">
+        <v>18.1885</v>
       </c>
     </row>
   </sheetData>
@@ -62491,7 +62557,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C940"/>
+  <dimension ref="A1:C941"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -72832,6 +72898,17 @@
       </c>
       <c r="C940">
         <v>52.2688</v>
+      </c>
+    </row>
+    <row r="941" spans="1:3">
+      <c r="A941" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B941">
+        <v>100</v>
+      </c>
+      <c r="C941">
+        <v>51.7577</v>
       </c>
     </row>
   </sheetData>
@@ -72841,7 +72918,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C940"/>
+  <dimension ref="A1:C941"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -83184,6 +83261,17 @@
         <v>100.5067</v>
       </c>
     </row>
+    <row r="941" spans="1:3">
+      <c r="A941" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B941">
+        <v>1</v>
+      </c>
+      <c r="C941">
+        <v>99.4226</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/cbr/data/cb_currency.xlsx
+++ b/LME/parser/cbr/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C941"/>
+  <dimension ref="A1:C942"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -10743,6 +10743,17 @@
       </c>
       <c r="C941">
         <v>81.9739</v>
+      </c>
+    </row>
+    <row r="942" spans="1:3">
+      <c r="A942" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B942">
+        <v>1</v>
+      </c>
+      <c r="C942">
+        <v>81.1255</v>
       </c>
     </row>
   </sheetData>
@@ -10752,7 +10763,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C941"/>
+  <dimension ref="A1:C942"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -21104,6 +21115,17 @@
       </c>
       <c r="C941">
         <v>91.9337</v>
+      </c>
+    </row>
+    <row r="942" spans="1:3">
+      <c r="A942" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B942">
+        <v>1</v>
+      </c>
+      <c r="C942">
+        <v>91.13639999999999</v>
       </c>
     </row>
   </sheetData>
@@ -21113,7 +21135,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C941"/>
+  <dimension ref="A1:C942"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -31465,6 +31487,17 @@
       </c>
       <c r="C941">
         <v>57.4637</v>
+      </c>
+    </row>
+    <row r="942" spans="1:3">
+      <c r="A942" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B942">
+        <v>1</v>
+      </c>
+      <c r="C942">
+        <v>56.9339</v>
       </c>
     </row>
   </sheetData>
@@ -31474,7 +31507,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C941"/>
+  <dimension ref="A1:C942"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -41826,6 +41859,17 @@
       </c>
       <c r="C941">
         <v>12.2806</v>
+      </c>
+    </row>
+    <row r="942" spans="1:3">
+      <c r="A942" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B942">
+        <v>1</v>
+      </c>
+      <c r="C942">
+        <v>12.146</v>
       </c>
     </row>
   </sheetData>
@@ -41835,7 +41879,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C941"/>
+  <dimension ref="A1:C942"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -52187,6 +52231,17 @@
       </c>
       <c r="C941">
         <v>109.7385</v>
+      </c>
+    </row>
+    <row r="942" spans="1:3">
+      <c r="A942" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B942">
+        <v>1</v>
+      </c>
+      <c r="C942">
+        <v>108.5784</v>
       </c>
     </row>
   </sheetData>
@@ -52196,7 +52251,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C941"/>
+  <dimension ref="A1:C942"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -62548,6 +62603,17 @@
       </c>
       <c r="C941">
         <v>18.1885</v>
+      </c>
+    </row>
+    <row r="942" spans="1:3">
+      <c r="A942" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B942">
+        <v>100</v>
+      </c>
+      <c r="C942">
+        <v>18.0837</v>
       </c>
     </row>
   </sheetData>
@@ -62557,7 +62623,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C941"/>
+  <dimension ref="A1:C942"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -72909,6 +72975,17 @@
       </c>
       <c r="C941">
         <v>51.7577</v>
+      </c>
+    </row>
+    <row r="942" spans="1:3">
+      <c r="A942" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B942">
+        <v>100</v>
+      </c>
+      <c r="C942">
+        <v>51.2771</v>
       </c>
     </row>
   </sheetData>
@@ -72918,7 +72995,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C941"/>
+  <dimension ref="A1:C942"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -83272,6 +83349,17 @@
         <v>99.4226</v>
       </c>
     </row>
+    <row r="942" spans="1:3">
+      <c r="A942" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B942">
+        <v>1</v>
+      </c>
+      <c r="C942">
+        <v>98.9456</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/cbr/data/cb_currency.xlsx
+++ b/LME/parser/cbr/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C942"/>
+  <dimension ref="A1:C943"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -10754,6 +10754,17 @@
       </c>
       <c r="C942">
         <v>81.1255</v>
+      </c>
+    </row>
+    <row r="943" spans="1:3">
+      <c r="A943" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B943">
+        <v>1</v>
+      </c>
+      <c r="C943">
+        <v>80.5381</v>
       </c>
     </row>
   </sheetData>
@@ -10763,7 +10774,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C942"/>
+  <dimension ref="A1:C943"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -21126,6 +21137,17 @@
       </c>
       <c r="C942">
         <v>91.13639999999999</v>
+      </c>
+    </row>
+    <row r="943" spans="1:3">
+      <c r="A943" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B943">
+        <v>1</v>
+      </c>
+      <c r="C943">
+        <v>90.24290000000001</v>
       </c>
     </row>
   </sheetData>
@@ -21135,7 +21157,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C942"/>
+  <dimension ref="A1:C943"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -31498,6 +31520,17 @@
       </c>
       <c r="C942">
         <v>56.9339</v>
+      </c>
+    </row>
+    <row r="943" spans="1:3">
+      <c r="A943" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B943">
+        <v>1</v>
+      </c>
+      <c r="C943">
+        <v>56.425</v>
       </c>
     </row>
   </sheetData>
@@ -31507,7 +31540,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C942"/>
+  <dimension ref="A1:C943"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -41870,6 +41903,17 @@
       </c>
       <c r="C942">
         <v>12.146</v>
+      </c>
+    </row>
+    <row r="943" spans="1:3">
+      <c r="A943" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B943">
+        <v>1</v>
+      </c>
+      <c r="C943">
+        <v>12.0557</v>
       </c>
     </row>
   </sheetData>
@@ -41879,7 +41923,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C942"/>
+  <dimension ref="A1:C943"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -52242,6 +52286,17 @@
       </c>
       <c r="C942">
         <v>108.5784</v>
+      </c>
+    </row>
+    <row r="943" spans="1:3">
+      <c r="A943" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B943">
+        <v>1</v>
+      </c>
+      <c r="C943">
+        <v>107.6231</v>
       </c>
     </row>
   </sheetData>
@@ -52251,7 +52306,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C942"/>
+  <dimension ref="A1:C943"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -62614,6 +62669,17 @@
       </c>
       <c r="C942">
         <v>18.0837</v>
+      </c>
+    </row>
+    <row r="943" spans="1:3">
+      <c r="A943" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B943">
+        <v>100</v>
+      </c>
+      <c r="C943">
+        <v>17.9797</v>
       </c>
     </row>
   </sheetData>
@@ -62623,7 +62689,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C942"/>
+  <dimension ref="A1:C943"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -72986,6 +73052,17 @@
       </c>
       <c r="C942">
         <v>51.2771</v>
+      </c>
+    </row>
+    <row r="943" spans="1:3">
+      <c r="A943" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B943">
+        <v>100</v>
+      </c>
+      <c r="C943">
+        <v>51.4785</v>
       </c>
     </row>
   </sheetData>
@@ -72995,7 +73072,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C942"/>
+  <dimension ref="A1:C943"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -83360,6 +83437,17 @@
         <v>98.9456</v>
       </c>
     </row>
+    <row r="943" spans="1:3">
+      <c r="A943" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B943">
+        <v>1</v>
+      </c>
+      <c r="C943">
+        <v>97.8473</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/cbr/data/cb_currency.xlsx
+++ b/LME/parser/cbr/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C943"/>
+  <dimension ref="A1:C944"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -10765,6 +10765,17 @@
       </c>
       <c r="C943">
         <v>80.5381</v>
+      </c>
+    </row>
+    <row r="944" spans="1:3">
+      <c r="A944" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B944">
+        <v>1</v>
+      </c>
+      <c r="C944">
+        <v>80.4909</v>
       </c>
     </row>
   </sheetData>
@@ -10774,7 +10785,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C943"/>
+  <dimension ref="A1:C944"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -21148,6 +21159,17 @@
       </c>
       <c r="C943">
         <v>90.24290000000001</v>
+      </c>
+    </row>
+    <row r="944" spans="1:3">
+      <c r="A944" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B944">
+        <v>1</v>
+      </c>
+      <c r="C944">
+        <v>90.09350000000001</v>
       </c>
     </row>
   </sheetData>
@@ -21157,7 +21179,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C943"/>
+  <dimension ref="A1:C944"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -31531,6 +31553,17 @@
       </c>
       <c r="C943">
         <v>56.425</v>
+      </c>
+    </row>
+    <row r="944" spans="1:3">
+      <c r="A944" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B944">
+        <v>1</v>
+      </c>
+      <c r="C944">
+        <v>56.5932</v>
       </c>
     </row>
   </sheetData>
@@ -31540,7 +31573,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C943"/>
+  <dimension ref="A1:C944"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -41914,6 +41947,17 @@
       </c>
       <c r="C943">
         <v>12.0557</v>
+      </c>
+    </row>
+    <row r="944" spans="1:3">
+      <c r="A944" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B944">
+        <v>1</v>
+      </c>
+      <c r="C944">
+        <v>12.068</v>
       </c>
     </row>
   </sheetData>
@@ -41923,7 +41967,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C943"/>
+  <dimension ref="A1:C944"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -52297,6 +52341,17 @@
       </c>
       <c r="C943">
         <v>107.6231</v>
+      </c>
+    </row>
+    <row r="944" spans="1:3">
+      <c r="A944" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B944">
+        <v>1</v>
+      </c>
+      <c r="C944">
+        <v>107.7532</v>
       </c>
     </row>
   </sheetData>
@@ -52306,7 +52361,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C943"/>
+  <dimension ref="A1:C944"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -62680,6 +62735,17 @@
       </c>
       <c r="C943">
         <v>17.9797</v>
+      </c>
+    </row>
+    <row r="944" spans="1:3">
+      <c r="A944" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B944">
+        <v>100</v>
+      </c>
+      <c r="C944">
+        <v>17.8452</v>
       </c>
     </row>
   </sheetData>
@@ -62689,7 +62755,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C943"/>
+  <dimension ref="A1:C944"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -73063,6 +73129,17 @@
       </c>
       <c r="C943">
         <v>51.4785</v>
+      </c>
+    </row>
+    <row r="944" spans="1:3">
+      <c r="A944" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B944">
+        <v>100</v>
+      </c>
+      <c r="C944">
+        <v>51.2029</v>
       </c>
     </row>
   </sheetData>
@@ -73072,7 +73149,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C943"/>
+  <dimension ref="A1:C944"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -83448,6 +83525,17 @@
         <v>97.8473</v>
       </c>
     </row>
+    <row r="944" spans="1:3">
+      <c r="A944" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B944">
+        <v>1</v>
+      </c>
+      <c r="C944">
+        <v>97.423</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/cbr/data/cb_currency.xlsx
+++ b/LME/parser/cbr/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C944"/>
+  <dimension ref="A1:C945"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -10776,6 +10776,17 @@
       </c>
       <c r="C944">
         <v>80.4909</v>
+      </c>
+    </row>
+    <row r="945" spans="1:3">
+      <c r="A945" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B945">
+        <v>1</v>
+      </c>
+      <c r="C945">
+        <v>80.5307</v>
       </c>
     </row>
   </sheetData>
@@ -10785,7 +10796,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C944"/>
+  <dimension ref="A1:C945"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -21170,6 +21181,17 @@
       </c>
       <c r="C944">
         <v>90.09350000000001</v>
+      </c>
+    </row>
+    <row r="945" spans="1:3">
+      <c r="A945" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B945">
+        <v>1</v>
+      </c>
+      <c r="C945">
+        <v>90.0977</v>
       </c>
     </row>
   </sheetData>
@@ -21179,7 +21201,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C944"/>
+  <dimension ref="A1:C945"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -31564,6 +31586,17 @@
       </c>
       <c r="C944">
         <v>56.5932</v>
+      </c>
+    </row>
+    <row r="945" spans="1:3">
+      <c r="A945" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B945">
+        <v>1</v>
+      </c>
+      <c r="C945">
+        <v>56.5406</v>
       </c>
     </row>
   </sheetData>
@@ -31573,7 +31606,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C944"/>
+  <dimension ref="A1:C945"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -41958,6 +41991,17 @@
       </c>
       <c r="C944">
         <v>12.068</v>
+      </c>
+    </row>
+    <row r="945" spans="1:3">
+      <c r="A945" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B945">
+        <v>1</v>
+      </c>
+      <c r="C945">
+        <v>12.0677</v>
       </c>
     </row>
   </sheetData>
@@ -41967,7 +42011,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C944"/>
+  <dimension ref="A1:C945"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -52352,6 +52396,17 @@
       </c>
       <c r="C944">
         <v>107.7532</v>
+      </c>
+    </row>
+    <row r="945" spans="1:3">
+      <c r="A945" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B945">
+        <v>1</v>
+      </c>
+      <c r="C945">
+        <v>107.4843</v>
       </c>
     </row>
   </sheetData>
@@ -52361,7 +52416,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C944"/>
+  <dimension ref="A1:C945"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -62746,6 +62801,17 @@
       </c>
       <c r="C944">
         <v>17.8452</v>
+      </c>
+    </row>
+    <row r="945" spans="1:3">
+      <c r="A945" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B945">
+        <v>100</v>
+      </c>
+      <c r="C945">
+        <v>17.8541</v>
       </c>
     </row>
   </sheetData>
@@ -62755,7 +62821,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C944"/>
+  <dimension ref="A1:C945"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -73140,6 +73206,17 @@
       </c>
       <c r="C944">
         <v>51.2029</v>
+      </c>
+    </row>
+    <row r="945" spans="1:3">
+      <c r="A945" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B945">
+        <v>100</v>
+      </c>
+      <c r="C945">
+        <v>51.082</v>
       </c>
     </row>
   </sheetData>
@@ -73149,7 +73226,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C944"/>
+  <dimension ref="A1:C945"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -83536,6 +83613,17 @@
         <v>97.423</v>
       </c>
     </row>
+    <row r="945" spans="1:3">
+      <c r="A945" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B945">
+        <v>1</v>
+      </c>
+      <c r="C945">
+        <v>97.20059999999999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/cbr/data/cb_currency.xlsx
+++ b/LME/parser/cbr/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C945"/>
+  <dimension ref="A1:C946"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -10787,6 +10787,17 @@
       </c>
       <c r="C945">
         <v>80.5307</v>
+      </c>
+    </row>
+    <row r="946" spans="1:3">
+      <c r="A946" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B946">
+        <v>1</v>
+      </c>
+      <c r="C946">
+        <v>80.8664</v>
       </c>
     </row>
   </sheetData>
@@ -10796,7 +10807,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C945"/>
+  <dimension ref="A1:C946"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -21192,6 +21203,17 @@
       </c>
       <c r="C945">
         <v>90.0977</v>
+      </c>
+    </row>
+    <row r="946" spans="1:3">
+      <c r="A946" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B946">
+        <v>1</v>
+      </c>
+      <c r="C946">
+        <v>90.166</v>
       </c>
     </row>
   </sheetData>
@@ -21201,7 +21223,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C945"/>
+  <dimension ref="A1:C946"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -31597,6 +31619,17 @@
       </c>
       <c r="C945">
         <v>56.5406</v>
+      </c>
+    </row>
+    <row r="946" spans="1:3">
+      <c r="A946" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B946">
+        <v>1</v>
+      </c>
+      <c r="C946">
+        <v>56.8814</v>
       </c>
     </row>
   </sheetData>
@@ -31606,7 +31639,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C945"/>
+  <dimension ref="A1:C946"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -42002,6 +42035,17 @@
       </c>
       <c r="C945">
         <v>12.0677</v>
+      </c>
+    </row>
+    <row r="946" spans="1:3">
+      <c r="A946" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B946">
+        <v>1</v>
+      </c>
+      <c r="C946">
+        <v>12.0816</v>
       </c>
     </row>
   </sheetData>
@@ -42011,7 +42055,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C945"/>
+  <dimension ref="A1:C946"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -52407,6 +52451,17 @@
       </c>
       <c r="C945">
         <v>107.4843</v>
+      </c>
+    </row>
+    <row r="946" spans="1:3">
+      <c r="A946" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B946">
+        <v>1</v>
+      </c>
+      <c r="C946">
+        <v>107.6574</v>
       </c>
     </row>
   </sheetData>
@@ -52416,7 +52471,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C945"/>
+  <dimension ref="A1:C946"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -62812,6 +62867,17 @@
       </c>
       <c r="C945">
         <v>17.8541</v>
+      </c>
+    </row>
+    <row r="946" spans="1:3">
+      <c r="A946" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B946">
+        <v>100</v>
+      </c>
+      <c r="C946">
+        <v>17.7483</v>
       </c>
     </row>
   </sheetData>
@@ -62821,7 +62887,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C945"/>
+  <dimension ref="A1:C946"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -73217,6 +73283,17 @@
       </c>
       <c r="C945">
         <v>51.082</v>
+      </c>
+    </row>
+    <row r="946" spans="1:3">
+      <c r="A946" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B946">
+        <v>100</v>
+      </c>
+      <c r="C946">
+        <v>51.2331</v>
       </c>
     </row>
   </sheetData>
@@ -73226,7 +73303,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C945"/>
+  <dimension ref="A1:C946"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -83624,6 +83701,17 @@
         <v>97.20059999999999</v>
       </c>
     </row>
+    <row r="946" spans="1:3">
+      <c r="A946" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B946">
+        <v>1</v>
+      </c>
+      <c r="C946">
+        <v>97.38249999999999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/cbr/data/cb_currency.xlsx
+++ b/LME/parser/cbr/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C946"/>
+  <dimension ref="A1:C947"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -10798,6 +10798,17 @@
       </c>
       <c r="C946">
         <v>80.8664</v>
+      </c>
+    </row>
+    <row r="947" spans="1:3">
+      <c r="A947" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B947">
+        <v>1</v>
+      </c>
+      <c r="C947">
+        <v>80.67610000000001</v>
       </c>
     </row>
   </sheetData>
@@ -10807,7 +10818,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C946"/>
+  <dimension ref="A1:C947"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -21214,6 +21225,17 @@
       </c>
       <c r="C946">
         <v>90.166</v>
+      </c>
+    </row>
+    <row r="947" spans="1:3">
+      <c r="A947" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B947">
+        <v>1</v>
+      </c>
+      <c r="C947">
+        <v>89.8167</v>
       </c>
     </row>
   </sheetData>
@@ -21223,7 +21245,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C946"/>
+  <dimension ref="A1:C947"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -31630,6 +31652,17 @@
       </c>
       <c r="C946">
         <v>56.8814</v>
+      </c>
+    </row>
+    <row r="947" spans="1:3">
+      <c r="A947" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B947">
+        <v>1</v>
+      </c>
+      <c r="C947">
+        <v>56.9009</v>
       </c>
     </row>
   </sheetData>
@@ -31639,7 +31672,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C946"/>
+  <dimension ref="A1:C947"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -42046,6 +42079,17 @@
       </c>
       <c r="C946">
         <v>12.0816</v>
+      </c>
+    </row>
+    <row r="947" spans="1:3">
+      <c r="A947" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B947">
+        <v>1</v>
+      </c>
+      <c r="C947">
+        <v>12.0844</v>
       </c>
     </row>
   </sheetData>
@@ -42055,7 +42099,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C946"/>
+  <dimension ref="A1:C947"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -52462,6 +52506,17 @@
       </c>
       <c r="C946">
         <v>107.6574</v>
+      </c>
+    </row>
+    <row r="947" spans="1:3">
+      <c r="A947" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B947">
+        <v>1</v>
+      </c>
+      <c r="C947">
+        <v>107.3073</v>
       </c>
     </row>
   </sheetData>
@@ -52471,7 +52526,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C946"/>
+  <dimension ref="A1:C947"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -62878,6 +62933,17 @@
       </c>
       <c r="C946">
         <v>17.7483</v>
+      </c>
+    </row>
+    <row r="947" spans="1:3">
+      <c r="A947" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B947">
+        <v>100</v>
+      </c>
+      <c r="C947">
+        <v>17.6499</v>
       </c>
     </row>
   </sheetData>
@@ -62887,7 +62953,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C946"/>
+  <dimension ref="A1:C947"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -73294,6 +73360,17 @@
       </c>
       <c r="C946">
         <v>51.2331</v>
+      </c>
+    </row>
+    <row r="947" spans="1:3">
+      <c r="A947" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B947">
+        <v>100</v>
+      </c>
+      <c r="C947">
+        <v>51.0705</v>
       </c>
     </row>
   </sheetData>
@@ -73303,7 +73380,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C946"/>
+  <dimension ref="A1:C947"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -83712,6 +83789,17 @@
         <v>97.38249999999999</v>
       </c>
     </row>
+    <row r="947" spans="1:3">
+      <c r="A947" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B947">
+        <v>1</v>
+      </c>
+      <c r="C947">
+        <v>97.3526</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/cbr/data/cb_currency.xlsx
+++ b/LME/parser/cbr/data/cb_currency.xlsx
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C947"/>
+  <dimension ref="A1:C948"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -10809,6 +10809,17 @@
       </c>
       <c r="C947">
         <v>80.67610000000001</v>
+      </c>
+    </row>
+    <row r="948" spans="1:3">
+      <c r="A948" s="2">
+        <v>46326</v>
+      </c>
+      <c r="B948">
+        <v>1</v>
+      </c>
+      <c r="C948">
+        <v>80.5573</v>
       </c>
     </row>
   </sheetData>
@@ -10818,7 +10829,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C947"/>
+  <dimension ref="A1:C948"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -21236,6 +21247,17 @@
       </c>
       <c r="C947">
         <v>89.8167</v>
+      </c>
+    </row>
+    <row r="948" spans="1:3">
+      <c r="A948" s="2">
+        <v>46326</v>
+      </c>
+      <c r="B948">
+        <v>1</v>
+      </c>
+      <c r="C948">
+        <v>89.66030000000001</v>
       </c>
     </row>
   </sheetData>
@@ -21245,7 +21267,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C947"/>
+  <dimension ref="A1:C948"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -31663,6 +31685,17 @@
       </c>
       <c r="C947">
         <v>56.9009</v>
+      </c>
+    </row>
+    <row r="948" spans="1:3">
+      <c r="A948" s="2">
+        <v>46326</v>
+      </c>
+      <c r="B948">
+        <v>1</v>
+      </c>
+      <c r="C948">
+        <v>56.7123</v>
       </c>
     </row>
   </sheetData>
@@ -31672,7 +31705,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C947"/>
+  <dimension ref="A1:C948"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -42090,6 +42123,17 @@
       </c>
       <c r="C947">
         <v>12.0844</v>
+      </c>
+    </row>
+    <row r="948" spans="1:3">
+      <c r="A948" s="2">
+        <v>46326</v>
+      </c>
+      <c r="B948">
+        <v>1</v>
+      </c>
+      <c r="C948">
+        <v>12.0873</v>
       </c>
     </row>
   </sheetData>
@@ -42099,7 +42143,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C947"/>
+  <dimension ref="A1:C948"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -52517,6 +52561,17 @@
       </c>
       <c r="C947">
         <v>107.3073</v>
+      </c>
+    </row>
+    <row r="948" spans="1:3">
+      <c r="A948" s="2">
+        <v>46326</v>
+      </c>
+      <c r="B948">
+        <v>1</v>
+      </c>
+      <c r="C948">
+        <v>107.7454</v>
       </c>
     </row>
   </sheetData>
@@ -52526,7 +52581,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C947"/>
+  <dimension ref="A1:C948"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -62944,6 +62999,17 @@
       </c>
       <c r="C947">
         <v>17.6499</v>
+      </c>
+    </row>
+    <row r="948" spans="1:3">
+      <c r="A948" s="2">
+        <v>46326</v>
+      </c>
+      <c r="B948">
+        <v>100</v>
+      </c>
+      <c r="C948">
+        <v>17.7552</v>
       </c>
     </row>
   </sheetData>
@@ -62953,7 +63019,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C947"/>
+  <dimension ref="A1:C948"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -73371,6 +73437,17 @@
       </c>
       <c r="C947">
         <v>51.0705</v>
+      </c>
+    </row>
+    <row r="948" spans="1:3">
+      <c r="A948" s="2">
+        <v>46326</v>
+      </c>
+      <c r="B948">
+        <v>100</v>
+      </c>
+      <c r="C948">
+        <v>51.1475</v>
       </c>
     </row>
   </sheetData>
@@ -73380,7 +73457,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C947"/>
+  <dimension ref="A1:C948"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -83800,6 +83877,17 @@
         <v>97.3526</v>
       </c>
     </row>
+    <row r="948" spans="1:3">
+      <c r="A948" s="2">
+        <v>46326</v>
+      </c>
+      <c r="B948">
+        <v>1</v>
+      </c>
+      <c r="C948">
+        <v>97.2092</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
